--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44656</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45443</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>46203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45731</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45148</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45272</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44683</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>46113</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45040</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45191</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>45027</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>46142</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>45002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>45049</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         <v>46206</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         <v>46253</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>46237</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45817</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44488</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44827</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>44816</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>44776</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
         <v>46142</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>44762</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>45392</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>45282</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>46246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>46262</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>45397</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>45197</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>45436</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6732,7 +6732,7 @@
         <v>44937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>45946</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>44862</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44477</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45581</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>45195</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>45034</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         <v>45012</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>44935</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>45902</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         <v>45911</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8343,7 +8343,7 @@
         <v>44967</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45314</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8553,7 +8553,7 @@
         <v>44886</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>44696</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8773,7 +8773,7 @@
         <v>45952</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8883,7 +8883,7 @@
         <v>46038</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>46063</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>46204</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46205</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>45513</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>45439</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>46237</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45802</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>44714</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>44656</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>46167</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44585</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44782</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10223,7 +10223,7 @@
         <v>44648</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44643</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         <v>44816</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44862</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         <v>44657</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44720</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>44651</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>44839</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>44757</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45338</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>45425</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44490</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
         <v>44615</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44956</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>45602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45280</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44651</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44531</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45487</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45460</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45002</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45582</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12020,7 +12020,7 @@
         <v>45432</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
         <v>45602</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12166,7 +12166,7 @@
         <v>45540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12317,7 +12317,7 @@
         <v>44686</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>45084</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45229</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>45176</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>45196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44676</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45346</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45159</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45240</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12979,7 +12979,7 @@
         <v>45562</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>45726</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45702</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45098</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44974</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45190</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45034</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45427</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44627</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45545</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>44532</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45010</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45084</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45114</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45362</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44805</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45352</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44614</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45173</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45751</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44862</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45894</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>44979</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>45159</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>45156</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45401</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45700</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45478</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45160</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>45876</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45258</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45758</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45241</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45677</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45896</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>44533</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>45905</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45715</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45728</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>44638</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45911</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45915</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45870</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45239</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45916</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45525</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45924</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45173</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44837</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>44998</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45427</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>45947</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45616</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>45952</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45952</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45956</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17562,7 +17562,7 @@
         <v>45170</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17635,7 +17635,7 @@
         <v>45747</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45149</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45978</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>45583</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>44657</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45978</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45600</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18161,7 +18161,7 @@
         <v>45981</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45988</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45213</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45261</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45261</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45992</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45995</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>45279</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>45084</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45398</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45225</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44777</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45427</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45226</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44916</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45559</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>44696</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46041</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>46041</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>46041</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>46041</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>44610</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45082</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>46043</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>46043</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45582</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>46175</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45096</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>45342</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20348,7 +20348,7 @@
         <v>45583</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46058</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>46063</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44869</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>46063</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>44814</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>46182</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>46182</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>44665</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>44756</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45126</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45349</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45349</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45478</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>45478</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45235</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>45195</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45225</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46190</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>46098</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21853,7 +21853,7 @@
         <v>45583</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21931,7 +21931,7 @@
         <v>45084</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45321</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>46202</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22150,7 +22150,7 @@
         <v>46199</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>46199</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>46199</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45397</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>46199</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>46199</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>46244</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>46244</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45387</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44982</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46199</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45487</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23182,7 +23182,7 @@
         <v>46204</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>46246</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23328,7 +23328,7 @@
         <v>46246</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>46246</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>45668</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>44636</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45880</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45432</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44839</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23849,7 +23849,7 @@
         <v>45502</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>46204</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>46246</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24068,7 +24068,7 @@
         <v>46246</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>46248</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>46205</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45518</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>46248</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45240</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>44862</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45272</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45728</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>46216</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>46216</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24886,7 +24886,7 @@
         <v>45258</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24964,7 +24964,7 @@
         <v>46216</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25042,7 +25042,7 @@
         <v>45686</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25115,7 +25115,7 @@
         <v>44610</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25188,7 +25188,7 @@
         <v>46204</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45198</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25344,7 +25344,7 @@
         <v>44496</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>46268</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>46255</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25568,7 +25568,7 @@
         <v>45513</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25641,7 +25641,7 @@
         <v>46273</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25714,7 +25714,7 @@
         <v>46167</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>46034</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46261</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>46237</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>46237</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>46237</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26172,7 +26172,7 @@
         <v>46237</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>44827</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45614</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>46237</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26479,7 +26479,7 @@
         <v>46237</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>46237</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>46237</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>46238</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>46238</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>46237</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45574</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         <v>46241</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>45432</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>46283</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45810</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45812</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45812</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>45812</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>44960</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27604,7 +27604,7 @@
         <v>44960</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         <v>45842</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>45576</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27828,7 +27828,7 @@
         <v>45728</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27906,7 +27906,7 @@
         <v>45875</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27979,7 +27979,7 @@
         <v>45876</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45876</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>45882</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45111</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28271,7 +28271,7 @@
         <v>44714</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28349,7 +28349,7 @@
         <v>44606</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28422,7 +28422,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28500,7 +28500,7 @@
         <v>44714</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>44722</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28656,7 +28656,7 @@
         <v>44740</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28734,7 +28734,7 @@
         <v>45946</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28812,7 +28812,7 @@
         <v>45978</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45992</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46246</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45197</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45720</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44656</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45443</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45731</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45148</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45565</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45272</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44683</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>46113</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45027</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45040</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45191</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45190</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45817</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>46206</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>46237</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45049</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>44488</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45282</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44776</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45392</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>46262</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44762</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44816</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45397</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>44862</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44477</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44886</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>46038</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45902</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45911</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>45802</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>46063</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44696</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44778</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45513</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>46204</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>45314</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>46237</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45012</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44967</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>45397</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45581</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45195</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44935</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>45439</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44585</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44782</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44648</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44816</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44657</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>44720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44651</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44757</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45387</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45213</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45467</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45321</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45229</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45562</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45239</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45478</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45279</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45432</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44862</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45235</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45487</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>46041</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>46041</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>46041</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>46041</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>46043</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>46043</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45540</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45896</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45362</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45349</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45349</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>46058</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45915</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>46063</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>46063</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45432</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44869</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45810</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45583</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>45583</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>46098</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45398</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45947</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45190</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45427</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45952</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45812</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44956</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45272</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45956</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45225</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45478</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45034</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44979</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45981</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45159</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>44791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45582</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45992</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44533</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45880</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45995</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44862</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45677</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45176</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45084</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45686</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45427</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45173</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45894</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45870</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44610</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44916</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45261</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45261</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45149</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44490</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45747</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45518</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45988</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45842</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44496</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45342</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45226</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45478</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45728</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>46175</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45397</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45156</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45241</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>46182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>46182</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45425</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>44532</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45170</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>46190</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45875</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45876</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45545</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45876</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45126</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45616</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>46199</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>46199</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45160</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46199</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>46199</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>46199</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>46199</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46202</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44686</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44665</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>46204</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46205</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44814</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45726</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>46204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45082</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44651</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45096</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>44696</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45427</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45401</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45084</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44657</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>46216</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46216</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>46216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45098</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45460</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45715</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>46268</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>46204</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>44805</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46167</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46255</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46273</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45352</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46261</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45502</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45346</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45728</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>46034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46237</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>46237</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46237</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>46237</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>44756</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>46237</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46237</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>46237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>46237</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45487</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>46238</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>46238</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>46241</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>46283</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44998</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>44627</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>45159</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>46244</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>46244</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44614</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44610</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46246</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45002</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>46248</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>46246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>46248</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>44974</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44839</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44837</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>44636</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>46246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45728</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45582</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45010</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45432</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45668</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45196</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45114</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>44615</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45525</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45240</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44982</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45602</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45758</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45173</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45583</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44676</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45240</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45225</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45513</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44827</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45614</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44714</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44606</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44722</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45111</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45258</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44714</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>44740</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45992</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>46246</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45197</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>45720</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44656</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46203</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45443</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45731</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>45148</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45565</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>45272</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44683</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>46113</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45027</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>45040</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>45191</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>45190</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4077,7 +4077,7 @@
         <v>45002</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45817</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45981</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45002</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>46206</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>46253</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>46237</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4974,7 +4974,7 @@
         <v>45049</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>44488</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45282</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44776</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>45392</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44937</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>46262</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44762</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>44816</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45397</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>45946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         <v>44862</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44477</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>44886</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>46038</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>45902</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>45911</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>45802</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>46063</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>44696</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44778</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>45034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>45513</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>46204</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>46205</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>45314</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>46237</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>45012</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         <v>44967</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>45397</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45581</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45195</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44935</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9419,7 +9419,7 @@
         <v>45439</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9524,7 +9524,7 @@
         <v>44714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>46167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44585</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44782</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44648</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44816</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44657</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>44720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44651</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>44757</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10667,7 +10667,7 @@
         <v>44757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45387</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45213</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45195</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45467</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45321</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45229</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45562</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>45239</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>45478</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11490,7 +11490,7 @@
         <v>45258</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45279</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45432</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44862</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>45574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>45235</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>45487</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12099,7 +12099,7 @@
         <v>45700</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45894</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>46041</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>46041</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>46041</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>46041</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>46043</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         <v>46043</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>45540</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>45896</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>45902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>45362</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13015,7 +13015,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13088,7 +13088,7 @@
         <v>45349</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13161,7 +13161,7 @@
         <v>45349</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>46058</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>45916</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>45915</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>44616</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13614,7 +13614,7 @@
         <v>46063</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>46063</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>45924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>45432</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>44869</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13989,7 +13989,7 @@
         <v>45338</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14062,7 +14062,7 @@
         <v>45810</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14135,7 +14135,7 @@
         <v>45583</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>45583</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45559</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>46098</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14437,7 +14437,7 @@
         <v>45398</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>45947</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45190</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44777</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>45427</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45952</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45812</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45952</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44956</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45272</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>45956</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15270,7 +15270,7 @@
         <v>45225</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>45478</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>45034</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45812</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>44979</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>45602</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>45981</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45159</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>44791</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>45582</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>45992</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44533</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45880</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45995</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45894</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16624,7 +16624,7 @@
         <v>44862</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45677</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
         <v>45176</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>45084</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>45686</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>44960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>44960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45427</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45173</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45894</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45870</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>44610</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>44916</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45261</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45261</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45149</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>44531</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>44490</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>45747</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45518</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>45988</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45842</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>44496</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45342</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45226</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45478</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45728</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45576</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>46175</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45397</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>44978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>45156</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>45198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>45241</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>46182</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>46182</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19453,7 +19453,7 @@
         <v>45425</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>44532</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45280</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>45170</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>46190</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45875</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45876</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45545</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45876</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45126</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45616</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>46199</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>46199</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45160</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46199</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>46199</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20646,7 +20646,7 @@
         <v>46199</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>46199</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>46199</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>46199</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45882</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46202</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44686</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>44665</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>46204</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>46205</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>44814</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21527,7 +21527,7 @@
         <v>45726</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>46204</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>45082</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44651</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45096</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>44696</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45427</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44638</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45401</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45084</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44657</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>46216</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46216</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>46216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45098</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>45460</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45715</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>46268</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>46204</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>44805</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46167</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>46255</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>46273</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45352</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46261</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>45502</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45346</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45728</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>46034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46237</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>46237</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>46237</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24011,7 +24011,7 @@
         <v>46237</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>44756</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>46237</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46237</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>46237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>46237</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>45487</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>46238</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>46238</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>46241</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>46283</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44998</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>44627</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>45159</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25141,7 +25141,7 @@
         <v>46244</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>46244</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>44614</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44610</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46246</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45002</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>46248</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>46246</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>46248</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>44974</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44839</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>44837</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>44636</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>46246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45728</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45582</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45010</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45432</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45668</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45196</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>45114</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>44615</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45525</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>45240</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44982</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45602</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45758</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45173</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45583</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>44676</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45240</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>45225</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45513</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44827</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45614</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>44714</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44606</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44722</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45111</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45258</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28355,7 +28355,7 @@
         <v>44714</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>44740</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>45946</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45992</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44656</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45731</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45148</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45443</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45272</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44683</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>46113</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45040</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45002</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46206</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>46237</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45049</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44488</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44816</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44776</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44762</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45392</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>46262</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45282</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>46246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>45397</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>45946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44862</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44477</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>44616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>45397</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45902</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46038</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45911</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45802</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>46063</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45034</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>45012</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44935</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45952</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44967</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45314</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45952</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44886</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>44696</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46204</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>46205</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>46237</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>45513</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45439</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         <v>44714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44656</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>46167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44585</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44782</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44648</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>44643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44816</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44862</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44657</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44651</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44757</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45338</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44615</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>44490</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45425</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11043,7 +11043,7 @@
         <v>44956</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45280</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11199,7 +11199,7 @@
         <v>44651</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11272,7 +11272,7 @@
         <v>45602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44531</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45460</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>45487</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45432</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         <v>45582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>45751</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45540</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>44827</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45614</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45602</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45467</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45700</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45894</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44686</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45084</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45896</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45902</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>46041</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>46041</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46041</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>46041</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>45229</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>46043</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46043</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45911</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45432</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45176</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45915</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45916</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45159</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45924</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45196</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>46058</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44676</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45346</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>46063</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>46063</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45240</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45562</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>45726</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45810</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45702</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>45947</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45098</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45952</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45952</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45812</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>45956</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45812</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>45190</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>45034</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45427</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>44627</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45545</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>46098</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45173</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44532</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45010</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45084</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45978</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45981</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45114</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>45362</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>44805</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45352</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44614</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45992</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45995</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>44960</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>44979</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45159</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45156</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44616</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45401</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45478</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45880</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45160</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>45758</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>45241</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>45677</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>44862</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45842</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45715</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45894</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45728</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>44638</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45239</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>45525</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45876</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45173</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>44837</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>44998</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>44533</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19006,7 +19006,7 @@
         <v>45576</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45728</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>45870</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19230,7 +19230,7 @@
         <v>45894</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45616</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>45427</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45170</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45875</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>45747</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>45149</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45988</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45583</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44657</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20043,7 +20043,7 @@
         <v>45876</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45600</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45876</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45226</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45882</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>46175</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45213</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>46182</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45261</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45261</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45279</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45084</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>46190</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45398</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45225</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>44777</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45427</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46202</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21465,7 +21465,7 @@
         <v>46199</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>46199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>46199</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>46199</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21757,7 +21757,7 @@
         <v>46199</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>46199</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>46199</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>44916</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>46199</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>46204</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45559</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>46204</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>46205</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>44696</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44610</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>45082</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>46216</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45582</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>46216</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45096</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46216</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45342</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>45583</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23174,7 +23174,7 @@
         <v>44869</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>44814</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>46204</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>44665</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>46268</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>46273</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>46167</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23695,7 +23695,7 @@
         <v>46034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46261</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>44756</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23919,7 +23919,7 @@
         <v>46237</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>46237</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24075,7 +24075,7 @@
         <v>45126</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24153,7 +24153,7 @@
         <v>46237</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24231,7 +24231,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>46237</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>46237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24465,7 +24465,7 @@
         <v>46237</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24543,7 +24543,7 @@
         <v>46237</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>46238</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>46238</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24767,7 +24767,7 @@
         <v>45349</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24840,7 +24840,7 @@
         <v>45349</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24913,7 +24913,7 @@
         <v>45478</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24991,7 +24991,7 @@
         <v>45478</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45235</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>46237</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>45195</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25303,7 +25303,7 @@
         <v>45225</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25376,7 +25376,7 @@
         <v>45583</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25454,7 +25454,7 @@
         <v>46283</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45084</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>45321</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>46241</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>46244</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>46244</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>46246</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>46246</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>45397</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>46246</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>46248</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45387</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>46293</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44982</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45487</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>46248</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>46295</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45668</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44636</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45432</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>44839</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45502</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>46297</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45518</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>46255</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27460,7 +27460,7 @@
         <v>45240</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>44862</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45728</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45258</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45686</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44610</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>45198</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44496</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>45513</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>45111</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44714</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28356,7 +28356,7 @@
         <v>44606</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>45258</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28507,7 +28507,7 @@
         <v>44714</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>44722</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28741,7 +28741,7 @@
         <v>45946</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>45992</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>45105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44656</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>45731</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45148</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45443</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         <v>45272</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
         <v>45565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>44683</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>46113</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>44593</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3618,7 +3618,7 @@
         <v>45190</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3731,7 +3731,7 @@
         <v>45040</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>46253</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>45191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>45027</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>45002</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45817</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         <v>45981</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>46206</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>46237</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>45049</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>44488</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>44827</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44816</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>45197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>44776</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44937</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>44762</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45392</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         <v>46262</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>45282</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>46246</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         <v>45397</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         <v>45436</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44937</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>45946</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         <v>44862</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44477</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         <v>44616</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7046,7 +7046,7 @@
         <v>45397</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>45581</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>45902</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>46038</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45911</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45802</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>46063</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>45034</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>45012</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44935</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>44778</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>45952</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44967</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45314</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>45952</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>44886</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>44696</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>46204</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>46205</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>46237</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 32547-2024</t>
+          <t>A 34597-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45513</v>
+        <v>46255</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9327,14 +9327,19 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -9361,49 +9366,53 @@
         <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/A 32547-2024 artfynd.xlsx", "A 32547-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/A 34597-2026 artfynd.xlsx", "A 34597-2026")</f>
         <v/>
       </c>
       <c r="X79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/A 32547-2024 karta.png", "A 32547-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/A 34597-2026 karta.png", "A 34597-2026")</f>
         <v/>
       </c>
       <c r="Y79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/A 32547-2024 georefererad karta.tif", "A 32547-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/A 34597-2026 georefererad karta.tif", "A 34597-2026")</f>
         <v/>
       </c>
       <c r="AA79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/A 32547-2024 FSC-klagomål.docx", "A 32547-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/A 34597-2026 FSC-klagomål.docx", "A 34597-2026")</f>
         <v/>
       </c>
       <c r="AB79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/A 32547-2024 FSC-klagomål mail.docx", "A 32547-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/A 34597-2026 FSC-klagomål mail.docx", "A 34597-2026")</f>
         <v/>
       </c>
       <c r="AC79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/A 32547-2024 tillsynsbegäran.docx", "A 32547-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/A 34597-2026 tillsynsbegäran.docx", "A 34597-2026")</f>
         <v/>
       </c>
       <c r="AD79">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/A 32547-2024 tillsynsbegäran mail.docx", "A 32547-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/A 34597-2026 tillsynsbegäran mail.docx", "A 34597-2026")</f>
+        <v/>
+      </c>
+      <c r="AE79">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/fåglar/A 34597-2026 prioriterade fågelarter.docx", "A 34597-2026")</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 20981-2024</t>
+          <t>A 32547-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9413,14 +9422,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45439</v>
+        <v>45513</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9433,13 +9442,13 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
         <v>1</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -9469,63 +9478,63 @@
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="W80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/A 20981-2024 artfynd.xlsx", "A 20981-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/A 32547-2024 artfynd.xlsx", "A 32547-2024")</f>
         <v/>
       </c>
       <c r="X80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/A 20981-2024 karta.png", "A 20981-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/A 32547-2024 karta.png", "A 32547-2024")</f>
         <v/>
       </c>
       <c r="Y80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/A 20981-2024 georefererad karta.tif", "A 20981-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/A 32547-2024 georefererad karta.tif", "A 32547-2024")</f>
         <v/>
       </c>
       <c r="AA80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/A 20981-2024 FSC-klagomål.docx", "A 20981-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/A 32547-2024 FSC-klagomål.docx", "A 32547-2024")</f>
         <v/>
       </c>
       <c r="AB80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/A 20981-2024 FSC-klagomål mail.docx", "A 20981-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/A 32547-2024 FSC-klagomål mail.docx", "A 32547-2024")</f>
         <v/>
       </c>
       <c r="AC80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/A 20981-2024 tillsynsbegäran.docx", "A 20981-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/A 32547-2024 tillsynsbegäran.docx", "A 32547-2024")</f>
         <v/>
       </c>
       <c r="AD80">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/A 20981-2024 tillsynsbegäran mail.docx", "A 20981-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/A 32547-2024 tillsynsbegäran mail.docx", "A 32547-2024")</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S 3020-2022</t>
+          <t>A 20981-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44714</v>
+        <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9537,13 +9546,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -9583,42 +9587,42 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="W81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/S 3020-2022 artfynd.xlsx", "S 3020-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/A 20981-2024 artfynd.xlsx", "A 20981-2024")</f>
         <v/>
       </c>
       <c r="X81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/S 3020-2022 karta.png", "S 3020-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/A 20981-2024 karta.png", "A 20981-2024")</f>
         <v/>
       </c>
       <c r="Y81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/S 3020-2022 georefererad karta.tif", "S 3020-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/A 20981-2024 georefererad karta.tif", "A 20981-2024")</f>
         <v/>
       </c>
       <c r="AA81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/S 3020-2022 FSC-klagomål.docx", "S 3020-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/A 20981-2024 FSC-klagomål.docx", "A 20981-2024")</f>
         <v/>
       </c>
       <c r="AB81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/S 3020-2022 FSC-klagomål mail.docx", "S 3020-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/A 20981-2024 FSC-klagomål mail.docx", "A 20981-2024")</f>
         <v/>
       </c>
       <c r="AC81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/S 3020-2022 tillsynsbegäran.docx", "S 3020-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/A 20981-2024 tillsynsbegäran.docx", "A 20981-2024")</f>
         <v/>
       </c>
       <c r="AD81">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/S 3020-2022 tillsynsbegäran mail.docx", "S 3020-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/A 20981-2024 tillsynsbegäran mail.docx", "A 20981-2024")</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>S 1792-2022</t>
+          <t>S 3020-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9628,14 +9632,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Åtgärd i nyckelbiotop</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44656</v>
+        <v>44714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9653,7 +9657,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -9693,42 +9697,42 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="W82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/S 1792-2022 artfynd.xlsx", "S 1792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/S 3020-2022 artfynd.xlsx", "S 3020-2022")</f>
         <v/>
       </c>
       <c r="X82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/S 1792-2022 karta.png", "S 1792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/S 3020-2022 karta.png", "S 3020-2022")</f>
         <v/>
       </c>
       <c r="Y82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/S 1792-2022 georefererad karta.tif", "S 1792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/S 3020-2022 georefererad karta.tif", "S 3020-2022")</f>
         <v/>
       </c>
       <c r="AA82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/S 1792-2022 FSC-klagomål.docx", "S 1792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/S 3020-2022 FSC-klagomål.docx", "S 3020-2022")</f>
         <v/>
       </c>
       <c r="AB82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/S 1792-2022 FSC-klagomål mail.docx", "S 1792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/S 3020-2022 FSC-klagomål mail.docx", "S 3020-2022")</f>
         <v/>
       </c>
       <c r="AC82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/S 1792-2022 tillsynsbegäran.docx", "S 1792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/S 3020-2022 tillsynsbegäran.docx", "S 3020-2022")</f>
         <v/>
       </c>
       <c r="AD82">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/S 1792-2022 tillsynsbegäran mail.docx", "S 1792-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/S 3020-2022 tillsynsbegäran mail.docx", "S 3020-2022")</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>S 1551-2026</t>
+          <t>S 1792-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9738,14 +9742,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Åtgärd i nyckelbiotop</t>
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46167</v>
+        <v>44656</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9763,16 +9767,16 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -9787,7 +9791,7 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -9803,59 +9807,59 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/S 1551-2026 artfynd.xlsx", "S 1551-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/S 1792-2022 artfynd.xlsx", "S 1792-2022")</f>
         <v/>
       </c>
       <c r="X83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/S 1551-2026 karta.png", "S 1551-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/S 1792-2022 karta.png", "S 1792-2022")</f>
         <v/>
       </c>
       <c r="Y83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/S 1551-2026 georefererad karta.tif", "S 1551-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/S 1792-2022 georefererad karta.tif", "S 1792-2022")</f>
         <v/>
       </c>
       <c r="AA83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/S 1551-2026 FSC-klagomål.docx", "S 1551-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/S 1792-2022 FSC-klagomål.docx", "S 1792-2022")</f>
         <v/>
       </c>
       <c r="AB83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/S 1551-2026 FSC-klagomål mail.docx", "S 1551-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/S 1792-2022 FSC-klagomål mail.docx", "S 1792-2022")</f>
         <v/>
       </c>
       <c r="AC83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/S 1551-2026 tillsynsbegäran.docx", "S 1551-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/S 1792-2022 tillsynsbegäran.docx", "S 1792-2022")</f>
         <v/>
       </c>
       <c r="AD83">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/S 1551-2026 tillsynsbegäran mail.docx", "S 1551-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/S 1792-2022 tillsynsbegäran mail.docx", "S 1792-2022")</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 3366-2022</t>
+          <t>S 1551-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44585</v>
+        <v>46167</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9867,8 +9871,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9877,7 +9886,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -9892,26 +9901,58 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U84" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="W84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/artfynd/S 1551-2026 artfynd.xlsx", "S 1551-2026")</f>
+        <v/>
+      </c>
+      <c r="X84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor/S 1551-2026 karta.png", "S 1551-2026")</f>
+        <v/>
+      </c>
+      <c r="Y84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/kartor_geotiff/S 1551-2026 georefererad karta.tif", "S 1551-2026")</f>
+        <v/>
+      </c>
+      <c r="AA84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomål/S 1551-2026 FSC-klagomål.docx", "S 1551-2026")</f>
+        <v/>
+      </c>
+      <c r="AB84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/klagomålsmail/S 1551-2026 FSC-klagomål mail.docx", "S 1551-2026")</f>
+        <v/>
+      </c>
+      <c r="AC84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsyn/S 1551-2026 tillsynsbegäran.docx", "S 1551-2026")</f>
+        <v/>
+      </c>
+      <c r="AD84">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1861/tillsynsmail/S 1551-2026 tillsynsbegäran mail.docx", "S 1551-2026")</f>
+        <v/>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32512-2022</t>
+          <t>A 3366-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9925,10 +9966,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44782</v>
+        <v>44585</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9941,7 +9982,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9984,7 +10025,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 13660-2022</t>
+          <t>A 32512-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9998,10 +10039,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44648</v>
+        <v>44782</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10013,13 +10054,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -10062,7 +10098,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13120-2022</t>
+          <t>A 13660-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10076,10 +10112,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44643</v>
+        <v>44648</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10091,8 +10127,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -10135,7 +10176,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 39725-2022</t>
+          <t>A 13120-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10149,10 +10190,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44816</v>
+        <v>44643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10165,7 +10206,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -10208,7 +10249,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 49645-2022</t>
+          <t>A 39725-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10222,10 +10263,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44862</v>
+        <v>44816</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10238,7 +10279,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -10281,7 +10322,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 15086-2022</t>
+          <t>A 49645-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10295,10 +10336,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44657</v>
+        <v>44862</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10311,7 +10352,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -10354,7 +10395,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23330-2022</t>
+          <t>A 15086-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10368,10 +10409,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44720</v>
+        <v>44657</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10384,7 +10425,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -10427,7 +10468,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 14345-2022</t>
+          <t>A 23330-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10441,10 +10482,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44651</v>
+        <v>44720</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10457,7 +10498,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -10500,7 +10541,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 30145-2022</t>
+          <t>A 14345-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10510,14 +10551,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44757</v>
+        <v>44651</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10529,13 +10570,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -10578,7 +10614,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44216-2022</t>
+          <t>A 30145-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10588,14 +10624,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44839</v>
+        <v>44757</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10607,8 +10643,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -10651,7 +10692,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 30144-2022</t>
+          <t>A 44216-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10661,14 +10702,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44757</v>
+        <v>44839</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10680,13 +10721,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -10729,7 +10765,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6366-2024</t>
+          <t>A 30144-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10739,14 +10775,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45338</v>
+        <v>44757</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10758,8 +10794,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -10802,7 +10843,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9126-2022</t>
+          <t>A 6366-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10816,10 +10857,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44615</v>
+        <v>45338</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10832,7 +10873,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10875,7 +10916,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 59176-2021</t>
+          <t>A 9126-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10889,10 +10930,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44490</v>
+        <v>44615</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10905,7 +10946,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10948,7 +10989,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 18556-2024</t>
+          <t>A 59176-2021</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10958,14 +10999,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45425</v>
+        <v>44490</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10977,13 +11018,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -11026,7 +11062,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 4587-2023</t>
+          <t>A 18556-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -11036,14 +11072,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44956</v>
+        <v>45425</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11061,7 +11097,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11104,7 +11140,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 64419-2023</t>
+          <t>A 4587-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -11118,10 +11154,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45280</v>
+        <v>44956</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11139,7 +11175,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11182,7 +11218,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 14333-2022</t>
+          <t>A 64419-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -11196,10 +11232,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44651</v>
+        <v>45280</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11211,8 +11247,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11255,7 +11296,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 50891-2024</t>
+          <t>A 14333-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -11269,10 +11310,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45602</v>
+        <v>44651</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11285,7 +11326,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -11328,7 +11369,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 69230-2021</t>
+          <t>A 50891-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -11338,14 +11379,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44531</v>
+        <v>45602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11357,13 +11398,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -11406,7 +11442,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24760-2024</t>
+          <t>A 69230-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11416,14 +11452,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45460</v>
+        <v>44531</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11435,8 +11471,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -11479,7 +11520,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13168-2023</t>
+          <t>A 24760-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11493,10 +11534,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45002</v>
+        <v>45460</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11508,13 +11549,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -11557,7 +11593,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 29907-2024</t>
+          <t>A 13168-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11571,10 +11607,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45487</v>
+        <v>45002</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11586,8 +11622,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>0.4</v>
+        <v>2.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -11630,7 +11671,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 34227-2022</t>
+          <t>A 29907-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11644,10 +11685,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44791</v>
+        <v>45487</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11659,13 +11700,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -11708,7 +11744,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 19709-2024</t>
+          <t>A 34227-2022</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11722,10 +11758,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45432</v>
+        <v>44791</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11737,8 +11773,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -11781,7 +11822,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 46602-2024</t>
+          <t>A 19709-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11795,10 +11836,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45582</v>
+        <v>45432</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11811,7 +11852,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11854,7 +11895,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 16441-2025</t>
+          <t>A 46602-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11868,10 +11909,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45751</v>
+        <v>45582</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11883,13 +11924,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11932,7 +11968,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 37277-2024</t>
+          <t>A 16441-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11946,10 +11982,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45540</v>
+        <v>45751</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11961,8 +11997,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -12005,7 +12046,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 41595-2022</t>
+          <t>A 37277-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -12019,10 +12060,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44827</v>
+        <v>45540</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12034,13 +12075,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -12083,7 +12119,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 53247-2024</t>
+          <t>A 41595-2022</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -12097,10 +12133,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45614</v>
+        <v>44827</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12112,8 +12148,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -12156,7 +12197,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 50893-2024</t>
+          <t>A 53247-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -12170,10 +12211,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45602</v>
+        <v>45614</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12186,7 +12227,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -12229,7 +12270,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 25805-2024</t>
+          <t>A 50893-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -12243,10 +12284,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45467</v>
+        <v>45602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12258,13 +12299,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -12307,7 +12343,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 6766-2025</t>
+          <t>A 25805-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -12321,10 +12357,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45700</v>
+        <v>45467</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12336,8 +12372,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12380,7 +12421,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40067-2025</t>
+          <t>A 6766-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12394,10 +12435,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45894</v>
+        <v>45700</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12409,13 +12450,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -12458,7 +12494,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 18512-2022</t>
+          <t>A 40067-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -12472,10 +12508,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44686</v>
+        <v>45894</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12487,8 +12523,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -12531,7 +12572,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 24628-2023</t>
+          <t>A 18512-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -12545,10 +12586,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45084</v>
+        <v>44686</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12561,7 +12602,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -12604,7 +12645,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 41468-2025</t>
+          <t>A 24628-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -12618,10 +12659,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45896</v>
+        <v>45084</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12634,7 +12675,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -12677,7 +12718,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41693-2025</t>
+          <t>A 41468-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -12691,10 +12732,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45902</v>
+        <v>45896</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12707,7 +12748,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -12750,7 +12791,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 3235-2026</t>
+          <t>A 41693-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -12764,10 +12805,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46041</v>
+        <v>45902</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12779,13 +12820,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -12828,7 +12864,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 3257-2026</t>
+          <t>A 3235-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12845,7 +12881,7 @@
         <v>46041</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12863,7 +12899,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12906,7 +12942,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 3236-2026</t>
+          <t>A 3257-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12923,7 +12959,7 @@
         <v>46041</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12941,7 +12977,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12984,7 +13020,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 42604-2025</t>
+          <t>A 3236-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12998,10 +13034,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45905</v>
+        <v>46041</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13013,8 +13049,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -13057,7 +13098,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 3259-2026</t>
+          <t>A 42604-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -13071,10 +13112,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46041</v>
+        <v>45905</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13086,13 +13127,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -13135,7 +13171,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 53329-2023</t>
+          <t>A 3259-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -13149,10 +13185,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45229</v>
+        <v>46041</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13164,8 +13200,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -13208,7 +13249,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 44616-2024</t>
+          <t>A 53329-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -13222,10 +13263,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45574</v>
+        <v>45229</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13238,7 +13279,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -13281,7 +13322,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 3896-2026</t>
+          <t>A 44616-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -13295,10 +13336,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46043</v>
+        <v>45574</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13310,13 +13351,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>6.8</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -13359,7 +13395,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 3897-2026</t>
+          <t>A 3896-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13376,7 +13412,7 @@
         <v>46043</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13394,7 +13430,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>11.3</v>
+        <v>6.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -13437,7 +13473,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 43379-2025</t>
+          <t>A 3897-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -13451,10 +13487,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45911</v>
+        <v>46043</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13468,11 +13504,11 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>11.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -13515,7 +13551,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19750-2024</t>
+          <t>A 43379-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -13525,14 +13561,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45432</v>
+        <v>45911</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13550,7 +13586,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -13593,7 +13629,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 41886-2023</t>
+          <t>A 19750-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -13603,14 +13639,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45176</v>
+        <v>45432</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13622,8 +13658,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -13666,7 +13707,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 44177-2025</t>
+          <t>A 41886-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -13680,10 +13721,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45915</v>
+        <v>45176</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13696,7 +13737,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>5.3</v>
+        <v>2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -13739,7 +13780,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 44305-2025</t>
+          <t>A 44177-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -13753,10 +13794,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45916</v>
+        <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13769,7 +13810,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.3</v>
+        <v>5.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -13812,7 +13853,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 37698-2023</t>
+          <t>A 44305-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -13826,10 +13867,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45159</v>
+        <v>45916</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13842,7 +13883,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13885,7 +13926,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 46160-2025</t>
+          <t>A 37698-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -13895,14 +13936,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45924</v>
+        <v>45159</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13914,13 +13955,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13963,7 +13999,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 46235-2023</t>
+          <t>A 46160-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13973,14 +14009,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45196</v>
+        <v>45924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13994,11 +14030,11 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>7</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -14041,7 +14077,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7238-2026</t>
+          <t>A 46235-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -14055,10 +14091,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46058</v>
+        <v>45196</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14072,11 +14108,11 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -14119,7 +14155,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 17003-2022</t>
+          <t>A 7238-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -14133,10 +14169,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44676</v>
+        <v>46058</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14148,8 +14184,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>2.5</v>
+        <v>5.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -14192,7 +14233,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 7492-2024</t>
+          <t>A 17003-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -14206,10 +14247,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45346</v>
+        <v>44676</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14222,7 +14263,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -14265,7 +14306,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 7991-2026</t>
+          <t>A 7492-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -14279,10 +14320,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46063</v>
+        <v>45346</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14295,7 +14336,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -14338,7 +14379,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7992-2026</t>
+          <t>A 7991-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -14355,7 +14396,7 @@
         <v>46063</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14368,7 +14409,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -14411,7 +14452,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 56270-2023</t>
+          <t>A 7992-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -14425,10 +14466,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45240</v>
+        <v>46063</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14441,7 +14482,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -14484,7 +14525,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 42156-2024</t>
+          <t>A 56270-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -14498,10 +14539,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45562</v>
+        <v>45240</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14514,7 +14555,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -14557,7 +14598,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 11358-2025</t>
+          <t>A 42156-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -14571,10 +14612,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45726</v>
+        <v>45562</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14586,13 +14627,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -14635,7 +14671,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 26842-2025</t>
+          <t>A 11358-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -14649,10 +14685,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45810</v>
+        <v>45726</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14664,8 +14700,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -14708,7 +14749,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 7191-2025</t>
+          <t>A 26842-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -14722,10 +14763,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45702</v>
+        <v>45810</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14738,7 +14779,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -14781,7 +14822,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8278-2023</t>
+          <t>A 7191-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -14795,10 +14836,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44974</v>
+        <v>45702</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14810,13 +14851,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -14859,7 +14895,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 50980-2025</t>
+          <t>A 8278-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -14873,10 +14909,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45947</v>
+        <v>44974</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14890,11 +14926,11 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14937,7 +14973,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 29735-2023</t>
+          <t>A 50980-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14947,14 +14983,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45098</v>
+        <v>45947</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14966,8 +15002,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -15010,7 +15051,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 51920-2025</t>
+          <t>A 29735-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -15020,14 +15061,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45952</v>
+        <v>45098</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15039,13 +15080,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -15088,7 +15124,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 51942-2025</t>
+          <t>A 51920-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -15105,7 +15141,7 @@
         <v>45952</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15123,7 +15159,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -15166,7 +15202,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 27146-2025</t>
+          <t>A 51942-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -15180,10 +15216,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45812</v>
+        <v>45952</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15195,8 +15231,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -15239,7 +15280,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 52959-2025</t>
+          <t>A 27146-2025</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -15253,10 +15294,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45956</v>
+        <v>45812</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15269,7 +15310,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -15312,7 +15353,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 27147-2025</t>
+          <t>A 52959-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -15326,10 +15367,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45812</v>
+        <v>45956</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15342,7 +15383,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -15385,7 +15426,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 27148-2025</t>
+          <t>A 27147-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -15402,7 +15443,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15415,7 +15456,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -15458,7 +15499,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 9663-2023</t>
+          <t>A 27148-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -15472,10 +15513,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>44978</v>
+        <v>45812</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15488,7 +15529,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -15531,7 +15572,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 44811-2023</t>
+          <t>A 9663-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -15545,10 +15586,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45190</v>
+        <v>44978</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15560,13 +15601,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>3.9</v>
+        <v>2.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -15609,7 +15645,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 17016-2023</t>
+          <t>A 44811-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -15623,10 +15659,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45034</v>
+        <v>45190</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15638,8 +15674,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -15682,7 +15723,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 18891-2024</t>
+          <t>A 17016-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -15696,10 +15737,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45427</v>
+        <v>45034</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15712,7 +15753,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -15755,7 +15796,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 10863-2022</t>
+          <t>A 18891-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -15769,10 +15810,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44627</v>
+        <v>45427</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15785,7 +15826,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6.9</v>
+        <v>2.5</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -15828,7 +15869,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 38344-2024</t>
+          <t>A 10863-2022</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -15842,10 +15883,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45545</v>
+        <v>44627</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15858,7 +15899,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.3</v>
+        <v>6.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -15901,7 +15942,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 13977-2026</t>
+          <t>A 38344-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -15915,10 +15956,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46098</v>
+        <v>45545</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15931,7 +15972,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15974,7 +16015,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 40968-2023</t>
+          <t>A 13977-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15984,14 +16025,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45173</v>
+        <v>46098</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16003,13 +16044,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -16052,7 +16088,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 69607-2021</t>
+          <t>A 40968-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -16062,14 +16098,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44532</v>
+        <v>45173</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16083,11 +16119,11 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -16130,7 +16166,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 14288-2023</t>
+          <t>A 69607-2021</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -16144,10 +16180,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45010</v>
+        <v>44532</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16159,8 +16195,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -16203,7 +16244,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 24801-2023</t>
+          <t>A 14288-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -16217,10 +16258,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45084</v>
+        <v>45010</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16232,13 +16273,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>5.1</v>
+        <v>2.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -16281,7 +16317,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 56890-2025</t>
+          <t>A 24801-2023</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -16291,14 +16327,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45978</v>
+        <v>45084</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16312,11 +16348,11 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -16359,7 +16395,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 57766-2025</t>
+          <t>A 56890-2025</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -16369,14 +16405,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45981</v>
+        <v>45978</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16388,8 +16424,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -16432,7 +16473,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 31290-2023</t>
+          <t>A 57766-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -16446,10 +16487,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45114</v>
+        <v>45981</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16505,7 +16546,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 9645-2024</t>
+          <t>A 31290-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -16519,10 +16560,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45362</v>
+        <v>45114</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16534,13 +16575,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -16583,7 +16619,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 36880-2022</t>
+          <t>A 9645-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -16597,10 +16633,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44805</v>
+        <v>45362</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16612,8 +16648,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -16656,7 +16697,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 8347-2024</t>
+          <t>A 36880-2022</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -16666,14 +16707,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45352</v>
+        <v>44805</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16685,13 +16726,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>9.1</v>
+        <v>2.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -16734,7 +16770,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8869-2022</t>
+          <t>A 8347-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -16744,14 +16780,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44614</v>
+        <v>45352</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16763,8 +16799,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>9.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -16807,7 +16848,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 59861-2025</t>
+          <t>A 8869-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16821,10 +16862,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45992</v>
+        <v>44614</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16836,13 +16877,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -16885,7 +16921,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 60558-2025</t>
+          <t>A 59861-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -16899,10 +16935,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45995</v>
+        <v>45992</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16914,8 +16950,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16958,7 +16999,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 5604-2023</t>
+          <t>A 60558-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16972,10 +17013,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44960</v>
+        <v>45995</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16988,7 +17029,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -17031,7 +17072,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 5608-2023</t>
+          <t>A 5604-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -17048,7 +17089,7 @@
         <v>44960</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17061,7 +17102,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -17104,7 +17145,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 9073-2023</t>
+          <t>A 5608-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -17118,10 +17159,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44979</v>
+        <v>44960</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17134,7 +17175,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -17177,7 +17218,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 37723-2023</t>
+          <t>A 9073-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -17191,10 +17232,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45159</v>
+        <v>44979</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17207,7 +17248,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -17250,7 +17291,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 37451-2023</t>
+          <t>A 37723-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -17260,14 +17301,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45156</v>
+        <v>45159</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17279,13 +17320,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>1.7</v>
+        <v>4.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -17328,7 +17364,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 9414-2022</t>
+          <t>A 37451-2023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -17338,14 +17374,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>44616</v>
+        <v>45156</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17359,11 +17395,11 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>8.9</v>
+        <v>1.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -17406,7 +17442,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 15523-2024</t>
+          <t>A 9414-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -17416,14 +17452,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45401</v>
+        <v>44616</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17437,11 +17473,11 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.6</v>
+        <v>8.9</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -17484,7 +17520,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 28535-2024</t>
+          <t>A 15523-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -17498,10 +17534,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45478</v>
+        <v>45401</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17519,7 +17555,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -17562,7 +17598,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37718-2025</t>
+          <t>A 28535-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -17572,14 +17608,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45880</v>
+        <v>45478</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17597,7 +17633,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -17640,7 +17676,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 38010-2023</t>
+          <t>A 37718-2025</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -17654,10 +17690,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45160</v>
+        <v>45880</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17669,8 +17705,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>9.199999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -17713,7 +17754,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 60082-2023</t>
+          <t>A 38010-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -17723,14 +17764,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45258</v>
+        <v>45160</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17742,13 +17783,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>2.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -17791,7 +17827,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 17700-2025</t>
+          <t>A 60082-2023</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -17801,14 +17837,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45758</v>
+        <v>45258</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17820,8 +17856,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -17864,7 +17905,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 56272-2023</t>
+          <t>A 17700-2025</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -17878,10 +17919,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45241</v>
+        <v>45758</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17894,7 +17935,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17937,7 +17978,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 2910-2025</t>
+          <t>A 56272-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17951,10 +17992,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45677</v>
+        <v>45241</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17967,7 +18008,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -18010,7 +18051,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 49684-2022</t>
+          <t>A 2910-2025</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -18024,10 +18065,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44862</v>
+        <v>45677</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18040,7 +18081,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -18083,7 +18124,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 33729-2025</t>
+          <t>A 49684-2022</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -18097,10 +18138,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45842</v>
+        <v>44862</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18112,13 +18153,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>7.5</v>
+        <v>2.3</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -18161,7 +18197,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 9814-2025</t>
+          <t>A 33729-2025</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -18175,10 +18211,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45715</v>
+        <v>45842</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18190,8 +18226,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>0.9</v>
+        <v>7.5</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -18234,7 +18275,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 40065-2025</t>
+          <t>A 9814-2025</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -18248,10 +18289,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45894</v>
+        <v>45715</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18263,13 +18304,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>3.8</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -18312,7 +18348,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 12018-2025</t>
+          <t>A 40065-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -18326,10 +18362,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45728</v>
+        <v>45894</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18347,7 +18383,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>0.3</v>
+        <v>3.8</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -18390,7 +18426,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 12471-2022</t>
+          <t>A 12018-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -18404,10 +18440,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44638</v>
+        <v>45728</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18419,8 +18455,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>2.2</v>
+        <v>0.3</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -18463,7 +18504,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 55851-2023</t>
+          <t>A 12471-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -18477,10 +18518,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45239</v>
+        <v>44638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18493,7 +18534,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -18536,7 +18577,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 34527-2024</t>
+          <t>A 55851-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -18550,10 +18591,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45525</v>
+        <v>45239</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18565,13 +18606,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -18614,7 +18650,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 37321-2025</t>
+          <t>A 34527-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -18628,10 +18664,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45876</v>
+        <v>45525</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18645,11 +18681,11 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -18692,7 +18728,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 40887-2023</t>
+          <t>A 37321-2025</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -18706,10 +18742,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45173</v>
+        <v>45876</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18721,8 +18757,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -18765,7 +18806,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 43679-2022</t>
+          <t>A 40887-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -18779,10 +18820,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44837</v>
+        <v>45173</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18795,7 +18836,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -18838,7 +18879,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 12133-2023</t>
+          <t>A 43679-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -18852,10 +18893,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44998</v>
+        <v>44837</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18868,7 +18909,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -18911,7 +18952,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 70160-2021</t>
+          <t>A 12133-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18925,10 +18966,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>44533</v>
+        <v>44998</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18940,13 +18981,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>14.7</v>
+        <v>1.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18989,7 +19025,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 45300-2024</t>
+          <t>A 70160-2021</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -19003,10 +19039,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45576</v>
+        <v>44533</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19018,8 +19054,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>1.6</v>
+        <v>14.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -19062,7 +19103,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 12008-2025</t>
+          <t>A 45300-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -19076,10 +19117,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45728</v>
+        <v>45576</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19091,13 +19132,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I207" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -19140,7 +19176,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 36619-2025</t>
+          <t>A 12008-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -19154,10 +19190,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45870</v>
+        <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19169,8 +19205,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -19213,7 +19254,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 40072-2025</t>
+          <t>A 36619-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -19227,10 +19268,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45894</v>
+        <v>45870</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19242,13 +19283,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -19291,7 +19327,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 54075-2024</t>
+          <t>A 40072-2025</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -19305,10 +19341,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45616</v>
+        <v>45894</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19320,8 +19356,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>7.7</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -19364,7 +19405,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 18893-2024</t>
+          <t>A 54075-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -19378,10 +19419,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45427</v>
+        <v>45616</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19394,7 +19435,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -19437,7 +19478,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 40551-2023</t>
+          <t>A 18893-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -19451,10 +19492,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45170</v>
+        <v>45427</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19467,7 +19508,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -19510,7 +19551,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 37054-2025</t>
+          <t>A 40551-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -19524,10 +19565,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45875</v>
+        <v>45170</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19540,7 +19581,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -19583,7 +19624,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 15591-2025</t>
+          <t>A 37054-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -19597,10 +19638,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45747</v>
+        <v>45875</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19613,7 +19654,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -19656,7 +19697,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 36081-2023</t>
+          <t>A 15591-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -19670,10 +19711,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45149</v>
+        <v>45747</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19686,7 +19727,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -19729,7 +19770,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 56839-2025</t>
+          <t>A 36081-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -19743,10 +19784,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45978</v>
+        <v>45149</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19759,7 +19800,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -19802,7 +19843,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 59165-2025</t>
+          <t>A 56839-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19812,14 +19853,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45988</v>
+        <v>45978</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19832,7 +19873,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -19875,7 +19916,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 46863-2024</t>
+          <t>A 59165-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -19885,14 +19926,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45583</v>
+        <v>45988</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19904,13 +19945,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19953,7 +19989,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 14928-2022</t>
+          <t>A 46863-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19963,14 +19999,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44657</v>
+        <v>45583</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19982,8 +20018,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -20026,7 +20067,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 37228-2025</t>
+          <t>A 14928-2022</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -20036,14 +20077,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45876</v>
+        <v>44657</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20056,7 +20097,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>16.2</v>
+        <v>3.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -20099,7 +20140,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 50237-2024</t>
+          <t>A 37228-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -20109,14 +20150,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45600</v>
+        <v>45876</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20128,13 +20169,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>16.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -20177,7 +20213,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 37229-2025</t>
+          <t>A 50237-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -20187,14 +20223,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45876</v>
+        <v>45600</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20206,8 +20242,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -20250,7 +20291,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 53012-2023</t>
+          <t>A 37229-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -20260,14 +20301,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45226</v>
+        <v>45876</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20279,13 +20320,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -20328,7 +20364,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 38179-2025</t>
+          <t>A 53012-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -20338,14 +20374,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45882</v>
+        <v>45226</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20357,8 +20393,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -20401,7 +20442,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 25119-2026</t>
+          <t>A 38179-2025</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -20415,10 +20456,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46175</v>
+        <v>45882</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20431,7 +20472,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -20474,7 +20515,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 51350-2023</t>
+          <t>A 25119-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -20488,10 +20529,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45213</v>
+        <v>46175</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20504,7 +20545,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -20547,7 +20588,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 26301-2026</t>
+          <t>A 51350-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -20561,10 +20602,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46182</v>
+        <v>45213</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20577,7 +20618,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -20620,7 +20661,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 26294-2026</t>
+          <t>A 26301-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -20637,7 +20678,7 @@
         <v>46182</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20650,7 +20691,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -20693,7 +20734,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 61057-2023</t>
+          <t>A 26294-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -20707,10 +20748,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45261</v>
+        <v>46182</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20722,13 +20763,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -20771,7 +20807,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 61058-2023</t>
+          <t>A 61057-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -20788,7 +20824,7 @@
         <v>45261</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20806,7 +20842,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -20849,7 +20885,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 64172-2023</t>
+          <t>A 61058-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -20863,10 +20899,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45279</v>
+        <v>45261</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20880,11 +20916,11 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20927,7 +20963,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 24624-2023</t>
+          <t>A 64172-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20941,10 +20977,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45084</v>
+        <v>45279</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20956,8 +20992,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -21000,7 +21041,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 27614-2026</t>
+          <t>A 24624-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -21014,10 +21055,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46190</v>
+        <v>45084</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21029,13 +21070,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -21078,7 +21114,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 14934-2024</t>
+          <t>A 27614-2026</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -21092,10 +21128,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45398</v>
+        <v>46190</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21105,6 +21141,11 @@
       <c r="G234" t="inlineStr">
         <is>
           <t>HALLSBERG</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I234" t="n">
@@ -21151,7 +21192,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 52710-2023</t>
+          <t>A 14934-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -21165,10 +21206,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45225</v>
+        <v>45398</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21181,7 +21222,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -21224,7 +21265,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 31893-2022</t>
+          <t>A 52710-2023</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -21238,10 +21279,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>44777</v>
+        <v>45225</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21253,13 +21294,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I236" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -21302,7 +21338,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 18892-2024</t>
+          <t>A 31893-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -21316,10 +21352,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45427</v>
+        <v>44777</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21331,8 +21367,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -21375,7 +21416,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 29326-2026</t>
+          <t>A 18892-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -21389,10 +21430,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46202</v>
+        <v>45427</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21405,7 +21446,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -21448,7 +21489,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 28945-2026</t>
+          <t>A 29326-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -21462,10 +21503,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21478,7 +21519,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -21521,7 +21562,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 28963-2026</t>
+          <t>A 28945-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -21538,7 +21579,7 @@
         <v>46199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21551,7 +21592,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -21594,7 +21635,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 28903-2026</t>
+          <t>A 28963-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -21611,7 +21652,7 @@
         <v>46199</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21624,7 +21665,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>5.2</v>
+        <v>2.1</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -21667,7 +21708,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 28913-2026</t>
+          <t>A 28903-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -21684,7 +21725,7 @@
         <v>46199</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21697,7 +21738,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -21740,7 +21781,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 28928-2026</t>
+          <t>A 28913-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -21757,7 +21798,7 @@
         <v>46199</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21770,7 +21811,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -21813,7 +21854,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 28941-2026</t>
+          <t>A 28928-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -21830,7 +21871,7 @@
         <v>46199</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21843,7 +21884,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -21886,7 +21927,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 28956-2026</t>
+          <t>A 28941-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -21903,7 +21944,7 @@
         <v>46199</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21916,7 +21957,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>6.3</v>
+        <v>4.6</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21959,7 +22000,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 61448-2022</t>
+          <t>A 28956-2026</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21969,14 +22010,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>44916</v>
+        <v>46199</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21988,13 +22029,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I246" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -22037,7 +22073,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 28932-2026</t>
+          <t>A 61448-2022</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -22047,14 +22083,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>46199</v>
+        <v>44916</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22066,8 +22102,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -22110,7 +22151,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 29718-2026</t>
+          <t>A 28932-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -22124,10 +22165,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46204</v>
+        <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22140,7 +22181,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -22183,7 +22224,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 41278-2024</t>
+          <t>A 29718-2026</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -22197,10 +22238,10 @@
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45559</v>
+        <v>46204</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22213,7 +22254,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -22256,7 +22297,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 29729-2026</t>
+          <t>A 41278-2024</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -22270,10 +22311,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>46204</v>
+        <v>45559</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22286,7 +22327,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -22329,7 +22370,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 29916-2026</t>
+          <t>A 29729-2026</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -22343,10 +22384,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22359,7 +22400,7 @@
         </is>
       </c>
       <c r="I251" t="n">
-        <v>8.699999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -22402,7 +22443,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 19849-2022</t>
+          <t>A 29916-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -22416,10 +22457,10 @@
         </is>
       </c>
       <c r="D252" s="1" t="n">
-        <v>44696</v>
+        <v>46205</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22431,13 +22472,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I252" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -22480,7 +22516,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 8606-2022</t>
+          <t>A 19849-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -22494,10 +22530,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>44610</v>
+        <v>44696</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22509,8 +22545,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I253" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -22553,7 +22594,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 24416-2023</t>
+          <t>A 8606-2022</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -22567,10 +22608,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45082</v>
+        <v>44610</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22583,7 +22624,7 @@
         </is>
       </c>
       <c r="I254" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -22626,7 +22667,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 31081-2026</t>
+          <t>A 24416-2023</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -22640,10 +22681,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46216</v>
+        <v>45082</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22655,13 +22696,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I255" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -22704,7 +22740,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 46580-2024</t>
+          <t>A 31081-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -22718,10 +22754,10 @@
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>45582</v>
+        <v>46216</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22733,8 +22769,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I256" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -22777,7 +22818,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 31079-2026</t>
+          <t>A 46580-2024</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -22791,10 +22832,10 @@
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>46216</v>
+        <v>45582</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22806,13 +22847,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I257" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -22855,7 +22891,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 27110-2023</t>
+          <t>A 31079-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -22869,10 +22905,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>45096</v>
+        <v>46216</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22884,8 +22920,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I258" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -22928,7 +22969,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 31082-2026</t>
+          <t>A 27110-2023</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -22942,10 +22983,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46216</v>
+        <v>45096</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22957,13 +22998,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I259" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -23006,7 +23042,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 6763-2024</t>
+          <t>A 31082-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -23020,10 +23056,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>45342</v>
+        <v>46216</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23035,8 +23071,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I260" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -23079,7 +23120,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 46835-2024</t>
+          <t>A 6763-2024</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -23093,10 +23134,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45583</v>
+        <v>45342</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23106,11 +23147,6 @@
       <c r="G261" t="inlineStr">
         <is>
           <t>HALLSBERG</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I261" t="n">
@@ -23157,7 +23193,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 51479-2022</t>
+          <t>A 46835-2024</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -23171,10 +23207,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>44869</v>
+        <v>45583</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23188,11 +23224,11 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I262" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -23235,7 +23271,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 38831-2022</t>
+          <t>A 51479-2022</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -23249,10 +23285,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>44814</v>
+        <v>44869</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23264,8 +23300,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I263" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -23308,7 +23349,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 29784-2026</t>
+          <t>A 38831-2022</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -23318,14 +23359,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>46204</v>
+        <v>44814</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23337,13 +23378,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I264" t="n">
-        <v>7.5</v>
+        <v>0.8</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -23386,7 +23422,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 16085-2022</t>
+          <t>A 29784-2026</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -23396,14 +23432,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44665</v>
+        <v>46204</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23415,8 +23451,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I265" t="n">
-        <v>5.1</v>
+        <v>7.5</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -23459,7 +23500,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 36408-2026</t>
+          <t>A 16085-2022</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -23473,10 +23514,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>46268</v>
+        <v>44665</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23489,7 +23530,7 @@
         </is>
       </c>
       <c r="I266" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -23532,7 +23573,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 36905-2026</t>
+          <t>A 36408-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -23546,10 +23587,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>46273</v>
+        <v>46268</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23562,7 +23603,7 @@
         </is>
       </c>
       <c r="I267" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -23605,7 +23646,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 23928-2026</t>
+          <t>A 36905-2026</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -23619,10 +23660,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>46167</v>
+        <v>46273</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23635,7 +23676,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -23678,7 +23719,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 1793-2026</t>
+          <t>A 23928-2026</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -23692,10 +23733,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>46034</v>
+        <v>46167</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23708,7 +23749,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>23.5</v>
+        <v>0.8</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -23751,7 +23792,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 35358-2026</t>
+          <t>A 1793-2026</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -23761,14 +23802,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>46261</v>
+        <v>46034</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23780,13 +23821,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I270" t="n">
-        <v>0.2</v>
+        <v>23.5</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -23829,7 +23865,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 29859-2022</t>
+          <t>A 35358-2026</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -23839,14 +23875,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>44756</v>
+        <v>46261</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23858,8 +23894,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I271" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -23902,7 +23943,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 32220-2026</t>
+          <t>A 29859-2022</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -23916,10 +23957,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>46237</v>
+        <v>44756</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23931,13 +23972,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I272" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -23980,7 +24016,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 32202-2026</t>
+          <t>A 32220-2026</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -23997,7 +24033,7 @@
         <v>46237</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24015,7 +24051,7 @@
         </is>
       </c>
       <c r="I273" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -24058,7 +24094,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 33097-2023</t>
+          <t>A 32202-2026</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -24068,14 +24104,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>45126</v>
+        <v>46237</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24093,7 +24129,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -24136,7 +24172,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 32189-2026</t>
+          <t>A 33097-2023</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -24146,14 +24182,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46237</v>
+        <v>45126</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24171,7 +24207,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -24214,7 +24250,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 32190-2026</t>
+          <t>A 32189-2026</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -24231,7 +24267,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24249,7 +24285,7 @@
         </is>
       </c>
       <c r="I276" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -24292,7 +24328,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 32186-2026</t>
+          <t>A 32190-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -24309,7 +24345,7 @@
         <v>46237</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24327,7 +24363,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -24370,7 +24406,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 32188-2026</t>
+          <t>A 32186-2026</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -24387,7 +24423,7 @@
         <v>46237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24405,7 +24441,7 @@
         </is>
       </c>
       <c r="I278" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -24448,7 +24484,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 32221-2026</t>
+          <t>A 32188-2026</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -24465,7 +24501,7 @@
         <v>46237</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24526,7 +24562,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 32191-2026</t>
+          <t>A 32221-2026</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -24543,7 +24579,7 @@
         <v>46237</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24561,7 +24597,7 @@
         </is>
       </c>
       <c r="I280" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -24604,7 +24640,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 32381-2026</t>
+          <t>A 32191-2026</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -24618,10 +24654,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24633,8 +24669,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I281" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -24677,7 +24718,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 32388-2026</t>
+          <t>A 32381-2026</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -24694,7 +24735,7 @@
         <v>46238</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24707,7 +24748,7 @@
         </is>
       </c>
       <c r="I282" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -24750,7 +24791,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 7784-2024</t>
+          <t>A 32388-2026</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -24764,10 +24805,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45349</v>
+        <v>46238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24780,7 +24821,7 @@
         </is>
       </c>
       <c r="I283" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -24823,7 +24864,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 7788-2024</t>
+          <t>A 7784-2024</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -24840,7 +24881,7 @@
         <v>45349</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24853,7 +24894,7 @@
         </is>
       </c>
       <c r="I284" t="n">
-        <v>1.2</v>
+        <v>3.8</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -24896,7 +24937,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 28537-2024</t>
+          <t>A 7788-2024</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -24906,14 +24947,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>45478</v>
+        <v>45349</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24925,13 +24966,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I285" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -24974,7 +25010,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 28540-2024</t>
+          <t>A 28537-2024</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -24991,7 +25027,7 @@
         <v>45478</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25009,7 +25045,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -25052,7 +25088,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 54679-2023</t>
+          <t>A 28540-2024</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -25062,14 +25098,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>45235</v>
+        <v>45478</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25087,7 +25123,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -25130,7 +25166,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 32193-2026</t>
+          <t>A 54679-2023</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -25144,10 +25180,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>46237</v>
+        <v>45235</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25165,7 +25201,7 @@
         </is>
       </c>
       <c r="I288" t="n">
-        <v>2.3</v>
+        <v>1.2</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -25208,7 +25244,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 45852-2023</t>
+          <t>A 32193-2026</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -25222,10 +25258,10 @@
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45195</v>
+        <v>46237</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25239,11 +25275,11 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I289" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -25286,7 +25322,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 52707-2023</t>
+          <t>A 45852-2023</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -25300,10 +25336,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>45225</v>
+        <v>45195</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25315,8 +25351,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I290" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -25359,7 +25400,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 46862-2024</t>
+          <t>A 52707-2023</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -25373,10 +25414,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45583</v>
+        <v>45225</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25388,13 +25429,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I291" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -25437,7 +25473,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 38592-2026</t>
+          <t>A 46862-2024</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -25451,10 +25487,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>46283</v>
+        <v>45583</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25464,6 +25500,11 @@
       <c r="G292" t="inlineStr">
         <is>
           <t>HALLSBERG</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I292" t="n">
@@ -25510,7 +25551,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 24629-2023</t>
+          <t>A 38592-2026</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -25524,10 +25565,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>45084</v>
+        <v>46283</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25540,7 +25581,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -25583,7 +25624,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 3799-2024</t>
+          <t>A 24629-2023</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -25597,10 +25638,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45321</v>
+        <v>45084</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25613,7 +25654,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -25656,7 +25697,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 32790-2026</t>
+          <t>A 3799-2024</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -25670,10 +25711,10 @@
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>46241</v>
+        <v>45321</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25685,13 +25726,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I295" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -25734,7 +25770,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A 33033-2026</t>
+          <t>A 32790-2026</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -25748,10 +25784,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25765,11 +25801,11 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I296" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -25812,7 +25848,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>A 33034-2026</t>
+          <t>A 33033-2026</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -25829,7 +25865,7 @@
         <v>46244</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25847,7 +25883,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -25890,7 +25926,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>A 33281-2026</t>
+          <t>A 33034-2026</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -25904,10 +25940,10 @@
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25919,8 +25955,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I298" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -25963,7 +26004,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>A 33329-2026</t>
+          <t>A 33281-2026</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -25980,7 +26021,7 @@
         <v>46246</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25993,7 +26034,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>2.3</v>
+        <v>7.3</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -26036,7 +26077,7 @@
     <row r="300" ht="15" customHeight="1">
       <c r="A300" t="inlineStr">
         <is>
-          <t>A 33184-2026</t>
+          <t>A 33329-2026</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -26053,7 +26094,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26066,7 +26107,7 @@
         </is>
       </c>
       <c r="I300" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -26109,7 +26150,7 @@
     <row r="301" ht="15" customHeight="1">
       <c r="A301" t="inlineStr">
         <is>
-          <t>A 33185-2026</t>
+          <t>A 33184-2026</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -26126,7 +26167,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26139,7 +26180,7 @@
         </is>
       </c>
       <c r="I301" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
@@ -26182,7 +26223,7 @@
     <row r="302" ht="15" customHeight="1">
       <c r="A302" t="inlineStr">
         <is>
-          <t>A 14676-2024</t>
+          <t>A 33185-2026</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -26196,10 +26237,10 @@
         </is>
       </c>
       <c r="D302" s="1" t="n">
-        <v>45397</v>
+        <v>46246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26212,7 +26253,7 @@
         </is>
       </c>
       <c r="I302" t="n">
-        <v>2.7</v>
+        <v>5.8</v>
       </c>
       <c r="J302" t="n">
         <v>0</v>
@@ -26255,7 +26296,7 @@
     <row r="303" ht="15" customHeight="1">
       <c r="A303" t="inlineStr">
         <is>
-          <t>A 33282-2026</t>
+          <t>A 14676-2024</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -26269,10 +26310,10 @@
         </is>
       </c>
       <c r="D303" s="1" t="n">
-        <v>46246</v>
+        <v>45397</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26285,7 +26326,7 @@
         </is>
       </c>
       <c r="I303" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -26328,7 +26369,7 @@
     <row r="304" ht="15" customHeight="1">
       <c r="A304" t="inlineStr">
         <is>
-          <t>A 33529-2026</t>
+          <t>A 33282-2026</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -26342,10 +26383,10 @@
         </is>
       </c>
       <c r="D304" s="1" t="n">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26358,7 +26399,7 @@
         </is>
       </c>
       <c r="I304" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J304" t="n">
         <v>0</v>
@@ -26401,7 +26442,7 @@
     <row r="305" ht="15" customHeight="1">
       <c r="A305" t="inlineStr">
         <is>
-          <t>A 13468-2024</t>
+          <t>A 33529-2026</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -26415,10 +26456,10 @@
         </is>
       </c>
       <c r="D305" s="1" t="n">
-        <v>45387</v>
+        <v>46248</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26431,7 +26472,7 @@
         </is>
       </c>
       <c r="I305" t="n">
-        <v>0.5</v>
+        <v>4.9</v>
       </c>
       <c r="J305" t="n">
         <v>0</v>
@@ -26474,7 +26515,7 @@
     <row r="306" ht="15" customHeight="1">
       <c r="A306" t="inlineStr">
         <is>
-          <t>A 40122-2026</t>
+          <t>A 13468-2024</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -26488,10 +26529,10 @@
         </is>
       </c>
       <c r="D306" s="1" t="n">
-        <v>46293</v>
+        <v>45387</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26503,13 +26544,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I306" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J306" t="n">
         <v>0</v>
@@ -26552,7 +26588,7 @@
     <row r="307" ht="15" customHeight="1">
       <c r="A307" t="inlineStr">
         <is>
-          <t>A 9569-2023</t>
+          <t>A 40122-2026</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -26566,10 +26602,10 @@
         </is>
       </c>
       <c r="D307" s="1" t="n">
-        <v>44982</v>
+        <v>46293</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26581,8 +26617,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I307" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -26625,7 +26666,7 @@
     <row r="308" ht="15" customHeight="1">
       <c r="A308" t="inlineStr">
         <is>
-          <t>A 29908-2024</t>
+          <t>A 9569-2023</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -26639,10 +26680,10 @@
         </is>
       </c>
       <c r="D308" s="1" t="n">
-        <v>45487</v>
+        <v>44982</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26655,7 +26696,7 @@
         </is>
       </c>
       <c r="I308" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J308" t="n">
         <v>0</v>
@@ -26698,7 +26739,7 @@
     <row r="309" ht="15" customHeight="1">
       <c r="A309" t="inlineStr">
         <is>
-          <t>A 33534-2026</t>
+          <t>A 29908-2024</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -26712,10 +26753,10 @@
         </is>
       </c>
       <c r="D309" s="1" t="n">
-        <v>46248</v>
+        <v>45487</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26728,7 +26769,7 @@
         </is>
       </c>
       <c r="I309" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J309" t="n">
         <v>0</v>
@@ -26771,7 +26812,7 @@
     <row r="310" ht="15" customHeight="1">
       <c r="A310" t="inlineStr">
         <is>
-          <t>A 40517-2026</t>
+          <t>A 33534-2026</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -26785,10 +26826,10 @@
         </is>
       </c>
       <c r="D310" s="1" t="n">
-        <v>46295</v>
+        <v>46248</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26801,7 +26842,7 @@
         </is>
       </c>
       <c r="I310" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -26844,7 +26885,7 @@
     <row r="311" ht="15" customHeight="1">
       <c r="A311" t="inlineStr">
         <is>
-          <t>A 1413-2025</t>
+          <t>A 40517-2026</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -26858,10 +26899,10 @@
         </is>
       </c>
       <c r="D311" s="1" t="n">
-        <v>45668</v>
+        <v>46295</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26874,7 +26915,7 @@
         </is>
       </c>
       <c r="I311" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J311" t="n">
         <v>0</v>
@@ -26917,7 +26958,7 @@
     <row r="312" ht="15" customHeight="1">
       <c r="A312" t="inlineStr">
         <is>
-          <t>A 12053-2022</t>
+          <t>A 1413-2025</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -26931,10 +26972,10 @@
         </is>
       </c>
       <c r="D312" s="1" t="n">
-        <v>44636</v>
+        <v>45668</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26947,7 +26988,7 @@
         </is>
       </c>
       <c r="I312" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="J312" t="n">
         <v>0</v>
@@ -26990,7 +27031,7 @@
     <row r="313" ht="15" customHeight="1">
       <c r="A313" t="inlineStr">
         <is>
-          <t>A 19751-2024</t>
+          <t>A 12053-2022</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -27000,14 +27041,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D313" s="1" t="n">
-        <v>45432</v>
+        <v>44636</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27019,13 +27060,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I313" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J313" t="n">
         <v>0</v>
@@ -27068,7 +27104,7 @@
     <row r="314" ht="15" customHeight="1">
       <c r="A314" t="inlineStr">
         <is>
-          <t>A 44210-2022</t>
+          <t>A 19751-2024</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -27078,14 +27114,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D314" s="1" t="n">
-        <v>44839</v>
+        <v>45432</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27097,8 +27133,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I314" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
@@ -27141,7 +27182,7 @@
     <row r="315" ht="15" customHeight="1">
       <c r="A315" t="inlineStr">
         <is>
-          <t>A 31094-2024</t>
+          <t>A 44210-2022</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -27151,14 +27192,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D315" s="1" t="n">
-        <v>45502</v>
+        <v>44839</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27171,7 +27212,7 @@
         </is>
       </c>
       <c r="I315" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -27214,7 +27255,7 @@
     <row r="316" ht="15" customHeight="1">
       <c r="A316" t="inlineStr">
         <is>
-          <t>A 41022-2026</t>
+          <t>A 31094-2024</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -27224,14 +27265,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D316" s="1" t="n">
-        <v>46297</v>
+        <v>45502</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27243,13 +27284,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I316" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
@@ -27292,7 +27328,7 @@
     <row r="317" ht="15" customHeight="1">
       <c r="A317" t="inlineStr">
         <is>
-          <t>A 33252-2024</t>
+          <t>A 41022-2026</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -27306,10 +27342,10 @@
         </is>
       </c>
       <c r="D317" s="1" t="n">
-        <v>45518</v>
+        <v>46297</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27321,8 +27357,13 @@
           <t>HALLSBERG</t>
         </is>
       </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I317" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -27365,7 +27406,7 @@
     <row r="318" ht="15" customHeight="1">
       <c r="A318" t="inlineStr">
         <is>
-          <t>A 34597-2026</t>
+          <t>A 33252-2024</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -27379,10 +27420,10 @@
         </is>
       </c>
       <c r="D318" s="1" t="n">
-        <v>46255</v>
+        <v>45518</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27394,13 +27435,8 @@
           <t>HALLSBERG</t>
         </is>
       </c>
-      <c r="H318" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I318" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -27460,7 +27496,7 @@
         <v>45240</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27533,7 +27569,7 @@
         <v>44862</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27606,7 +27642,7 @@
         <v>45272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27679,7 +27715,7 @@
         <v>45728</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27757,7 +27793,7 @@
         <v>45258</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27835,7 +27871,7 @@
         <v>45686</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27908,7 +27944,7 @@
         <v>44610</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27981,7 +28017,7 @@
         <v>45198</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28059,7 +28095,7 @@
         <v>44496</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28132,7 +28168,7 @@
         <v>45513</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28205,7 +28241,7 @@
         <v>45111</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28278,7 +28314,7 @@
         <v>44714</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28356,7 +28392,7 @@
         <v>44606</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28429,7 +28465,7 @@
         <v>45258</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28507,7 +28543,7 @@
         <v>44714</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28585,7 +28621,7 @@
         <v>44722</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28663,7 +28699,7 @@
         <v>44740</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28741,7 +28777,7 @@
         <v>45946</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28819,7 +28855,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28897,7 +28933,7 @@
         <v>45992</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>318.7</v>
       </c>
       <c r="J2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
         <v>16</v>
@@ -649,13 +649,13 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
@@ -699,6 +699,7 @@
 Brudborste
 Mattlummer
 Spillkråka
+Tjäder
 Grönsiska
 Havsörn
 Kungsfågel
@@ -763,7 +764,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -814,10 +815,10 @@
         <v>39</v>
       </c>
       <c r="T3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
@@ -915,7 +916,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1039,7 +1040,7 @@
         <v>45352</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1166,7 +1167,7 @@
         <v>45263</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1284,7 +1285,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1406,7 +1407,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1526,7 +1527,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1646,7 +1647,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1766,7 +1767,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1891,7 +1892,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2009,7 +2010,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2127,7 +2128,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2246,7 +2247,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2368,7 +2369,7 @@
         <v>46301</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2485,7 +2486,7 @@
         <v>45105</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2600,7 +2601,7 @@
         <v>44656</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2716,7 +2717,7 @@
         <v>45731</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2835,7 @@
         <v>45148</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2944,7 +2945,7 @@
         <v>45443</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3063,7 +3064,7 @@
         <v>46203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3173,7 +3174,7 @@
         <v>45565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3287,7 +3288,7 @@
         <v>45272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3396,7 +3397,7 @@
         <v>44683</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3509,7 +3510,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3623,7 +3624,7 @@
         <v>46113</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3736,7 +3737,7 @@
         <v>44593</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3849,7 +3850,7 @@
         <v>45027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3966,7 +3967,7 @@
         <v>45191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4083,7 +4084,7 @@
         <v>45190</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4196,7 +4197,7 @@
         <v>45040</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4308,7 +4309,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4421,7 +4422,7 @@
         <v>46302</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4533,7 +4534,7 @@
         <v>45049</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4640,7 +4641,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4756,7 +4757,7 @@
         <v>45817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4872,7 +4873,7 @@
         <v>45034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4979,7 +4980,7 @@
         <v>45981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5090,7 +5091,7 @@
         <v>45002</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5202,7 +5203,7 @@
         <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5313,7 +5314,7 @@
         <v>46237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5425,7 +5426,7 @@
         <v>44488</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5535,7 +5536,7 @@
         <v>44827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5646,7 +5647,7 @@
         <v>44776</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5756,7 +5757,7 @@
         <v>45392</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5862,7 +5863,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5973,7 +5974,7 @@
         <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6088,7 +6089,7 @@
         <v>45397</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6199,7 +6200,7 @@
         <v>45197</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6309,7 +6310,7 @@
         <v>44762</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6415,7 +6416,7 @@
         <v>44816</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6525,7 +6526,7 @@
         <v>46246</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6631,7 +6632,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6742,7 +6743,7 @@
         <v>45436</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6853,7 +6854,7 @@
         <v>44937</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6959,7 +6960,7 @@
         <v>45946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7070,7 +7071,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7179,7 +7180,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7284,7 +7285,7 @@
         <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7394,7 +7395,7 @@
         <v>45581</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7504,7 +7505,7 @@
         <v>45195</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7614,7 +7615,7 @@
         <v>44935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7719,7 +7720,7 @@
         <v>44886</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7829,7 +7830,7 @@
         <v>45902</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7934,7 +7935,7 @@
         <v>45439</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8039,7 +8040,7 @@
         <v>45911</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8149,7 +8150,7 @@
         <v>45034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8254,7 +8255,7 @@
         <v>45513</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8359,7 +8360,7 @@
         <v>45802</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8473,7 +8474,7 @@
         <v>44696</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8583,7 +8584,7 @@
         <v>45314</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8688,7 +8689,7 @@
         <v>44778</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8793,7 +8794,7 @@
         <v>45012</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8898,7 +8899,7 @@
         <v>44967</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9003,7 +9004,7 @@
         <v>45952</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9113,7 +9114,7 @@
         <v>46038</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9223,7 +9224,7 @@
         <v>46063</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9328,7 +9329,7 @@
         <v>45952</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9438,7 +9439,7 @@
         <v>46204</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9543,7 +9544,7 @@
         <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9653,7 +9654,7 @@
         <v>46237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,7 +9764,7 @@
         <v>46255</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9877,7 +9878,7 @@
         <v>44714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9987,7 +9988,7 @@
         <v>44656</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10097,7 +10098,7 @@
         <v>46167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10207,7 +10208,7 @@
         <v>44585</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10280,7 +10281,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10353,7 +10354,7 @@
         <v>44648</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10431,7 +10432,7 @@
         <v>44643</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10504,7 +10505,7 @@
         <v>44720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10577,7 +10578,7 @@
         <v>44757</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10655,7 +10656,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10728,7 +10729,7 @@
         <v>44651</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10801,7 +10802,7 @@
         <v>44757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10879,7 +10880,7 @@
         <v>44862</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10952,7 +10953,7 @@
         <v>44657</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11025,7 +11026,7 @@
         <v>44839</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11098,7 +11099,7 @@
         <v>45321</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11171,7 +11172,7 @@
         <v>44615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11244,7 +11245,7 @@
         <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11317,7 +11318,7 @@
         <v>45261</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11395,7 +11396,7 @@
         <v>45261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11473,7 +11474,7 @@
         <v>45525</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11551,7 +11552,7 @@
         <v>45387</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11624,7 +11625,7 @@
         <v>45213</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11697,7 +11698,7 @@
         <v>44531</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11775,7 +11776,7 @@
         <v>44490</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11848,7 +11849,7 @@
         <v>45518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11921,7 +11922,7 @@
         <v>45240</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11994,7 +11995,7 @@
         <v>45229</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12067,7 +12068,7 @@
         <v>45562</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12140,7 +12141,7 @@
         <v>45195</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12218,7 +12219,7 @@
         <v>45239</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12291,7 +12292,7 @@
         <v>45467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12369,7 +12370,7 @@
         <v>45258</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12447,7 +12448,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12520,7 +12521,7 @@
         <v>45342</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12593,7 +12594,7 @@
         <v>44982</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12666,7 +12667,7 @@
         <v>45478</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12744,7 +12745,7 @@
         <v>45602</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12817,7 +12818,7 @@
         <v>45758</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12890,7 +12891,7 @@
         <v>45173</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12968,7 +12969,7 @@
         <v>45583</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13046,7 +13047,7 @@
         <v>45258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13124,7 +13125,7 @@
         <v>45279</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13202,7 +13203,7 @@
         <v>44862</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13275,7 +13276,7 @@
         <v>45478</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13353,7 +13354,7 @@
         <v>45751</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13431,7 +13432,7 @@
         <v>44676</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13504,7 +13505,7 @@
         <v>45700</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13577,7 +13578,7 @@
         <v>45397</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13650,7 +13651,7 @@
         <v>44978</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13723,7 +13724,7 @@
         <v>45894</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13801,7 +13802,7 @@
         <v>45240</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13874,7 +13875,7 @@
         <v>45235</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13952,7 +13953,7 @@
         <v>45896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14025,7 +14026,7 @@
         <v>45487</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14098,7 +14099,7 @@
         <v>45902</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14171,7 +14172,7 @@
         <v>45156</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14249,7 +14250,7 @@
         <v>45905</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14322,7 +14323,7 @@
         <v>45540</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14395,7 +14396,7 @@
         <v>45225</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14468,7 +14469,7 @@
         <v>45084</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14541,7 +14542,7 @@
         <v>45198</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14619,7 +14620,7 @@
         <v>45241</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14692,7 +14693,7 @@
         <v>45911</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14770,7 +14771,7 @@
         <v>45362</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14848,7 +14849,7 @@
         <v>45916</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14921,7 +14922,7 @@
         <v>45513</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14994,7 +14995,7 @@
         <v>45915</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15067,7 +15068,7 @@
         <v>45425</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15145,7 +15146,7 @@
         <v>45349</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15218,7 +15219,7 @@
         <v>45349</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15291,7 +15292,7 @@
         <v>44532</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15369,7 +15370,7 @@
         <v>45280</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15447,7 +15448,7 @@
         <v>44616</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15525,7 +15526,7 @@
         <v>45170</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15598,7 +15599,7 @@
         <v>45924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15676,7 +15677,7 @@
         <v>45545</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15749,7 +15750,7 @@
         <v>44827</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15827,7 +15828,7 @@
         <v>45432</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15900,7 +15901,7 @@
         <v>45126</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15978,7 +15979,7 @@
         <v>45614</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16051,7 +16052,7 @@
         <v>44869</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16129,7 +16130,7 @@
         <v>45432</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16207,7 +16208,7 @@
         <v>45574</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16280,7 +16281,7 @@
         <v>45616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16353,7 +16354,7 @@
         <v>45160</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16426,7 +16427,7 @@
         <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16499,7 +16500,7 @@
         <v>45583</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16577,7 +16578,7 @@
         <v>45600</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16655,7 +16656,7 @@
         <v>44686</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16728,7 +16729,7 @@
         <v>44665</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16801,7 +16802,7 @@
         <v>45583</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16879,7 +16880,7 @@
         <v>44814</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16952,7 +16953,7 @@
         <v>45559</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17025,7 +17026,7 @@
         <v>45726</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17103,7 +17104,7 @@
         <v>45082</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17176,7 +17177,7 @@
         <v>44651</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17249,7 +17250,7 @@
         <v>45096</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17322,7 +17323,7 @@
         <v>45398</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17395,7 +17396,7 @@
         <v>45810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17468,7 +17469,7 @@
         <v>44696</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17546,7 +17547,7 @@
         <v>45190</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17624,7 +17625,7 @@
         <v>44777</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17702,7 +17703,7 @@
         <v>45427</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17775,7 +17776,7 @@
         <v>45812</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17848,7 +17849,7 @@
         <v>45427</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17921,7 +17922,7 @@
         <v>45812</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17994,7 +17995,7 @@
         <v>45812</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18067,7 +18068,7 @@
         <v>44638</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18140,7 +18141,7 @@
         <v>44956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18218,7 +18219,7 @@
         <v>45401</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18296,7 +18297,7 @@
         <v>45272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18369,7 +18370,7 @@
         <v>45084</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18442,7 +18443,7 @@
         <v>45225</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18515,7 +18516,7 @@
         <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18593,7 +18594,7 @@
         <v>45034</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18666,7 +18667,7 @@
         <v>45947</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18744,7 +18745,7 @@
         <v>44979</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18817,7 +18818,7 @@
         <v>44960</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18890,7 +18891,7 @@
         <v>44960</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18963,7 +18964,7 @@
         <v>44657</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19036,7 +19037,7 @@
         <v>45952</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19114,7 +19115,7 @@
         <v>45952</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19192,7 +19193,7 @@
         <v>45602</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19265,7 +19266,7 @@
         <v>45956</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19338,7 +19339,7 @@
         <v>45098</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19411,7 +19412,7 @@
         <v>45842</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19489,7 +19490,7 @@
         <v>45159</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19562,7 +19563,7 @@
         <v>44791</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19640,7 +19641,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19713,7 +19714,7 @@
         <v>45582</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19786,7 +19787,7 @@
         <v>45715</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19859,7 +19860,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19937,7 +19938,7 @@
         <v>44805</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20010,7 +20011,7 @@
         <v>45728</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20088,7 +20089,7 @@
         <v>45576</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20161,7 +20162,7 @@
         <v>45677</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20234,7 +20235,7 @@
         <v>45176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20307,7 +20308,7 @@
         <v>45084</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20380,7 +20381,7 @@
         <v>45875</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20453,7 +20454,7 @@
         <v>45876</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20526,7 +20527,7 @@
         <v>45352</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20604,7 +20605,7 @@
         <v>45876</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20677,7 +20678,7 @@
         <v>45981</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20750,7 +20751,7 @@
         <v>45084</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20828,7 +20829,7 @@
         <v>45502</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20901,7 +20902,7 @@
         <v>45346</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20974,7 +20975,7 @@
         <v>45882</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21047,7 +21048,7 @@
         <v>45728</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21125,7 +21126,7 @@
         <v>45686</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21198,7 +21199,7 @@
         <v>46098</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21271,7 +21272,7 @@
         <v>44756</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21344,7 +21345,7 @@
         <v>45173</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21417,7 +21418,7 @@
         <v>45487</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21490,7 +21491,7 @@
         <v>44610</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21563,7 +21564,7 @@
         <v>44916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21641,7 +21642,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21719,7 +21720,7 @@
         <v>44998</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21792,7 +21793,7 @@
         <v>44627</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21865,7 +21866,7 @@
         <v>45995</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21938,7 +21939,7 @@
         <v>45159</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22011,7 +22012,7 @@
         <v>44614</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22084,7 +22085,7 @@
         <v>44610</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22157,7 +22158,7 @@
         <v>45002</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22235,7 +22236,7 @@
         <v>44974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22313,7 +22314,7 @@
         <v>44839</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22386,7 +22387,7 @@
         <v>44837</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22459,7 +22460,7 @@
         <v>44636</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22532,7 +22533,7 @@
         <v>44533</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22610,7 +22611,7 @@
         <v>45880</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22688,7 +22689,7 @@
         <v>45876</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22766,7 +22767,7 @@
         <v>45728</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22844,7 +22845,7 @@
         <v>45894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22922,7 +22923,7 @@
         <v>44862</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22995,7 +22996,7 @@
         <v>45582</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23068,7 +23069,7 @@
         <v>45010</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23141,7 +23142,7 @@
         <v>45432</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23219,7 +23220,7 @@
         <v>45668</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23292,7 +23293,7 @@
         <v>46041</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23370,7 +23371,7 @@
         <v>46041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23448,7 +23449,7 @@
         <v>45196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23526,7 +23527,7 @@
         <v>46041</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23604,7 +23605,7 @@
         <v>46041</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23682,7 +23683,7 @@
         <v>45114</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23755,7 +23756,7 @@
         <v>46043</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23833,7 +23834,7 @@
         <v>46043</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23911,7 +23912,7 @@
         <v>45427</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23984,7 +23985,7 @@
         <v>45894</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24062,7 +24063,7 @@
         <v>46058</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24140,7 +24141,7 @@
         <v>45870</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24213,7 +24214,7 @@
         <v>46063</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24286,7 +24287,7 @@
         <v>46063</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24359,7 +24360,7 @@
         <v>45149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24432,7 +24433,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24505,7 +24506,7 @@
         <v>45747</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24578,7 +24579,7 @@
         <v>45988</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24651,7 +24652,7 @@
         <v>45226</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24729,7 +24730,7 @@
         <v>46175</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24802,7 +24803,7 @@
         <v>46182</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24875,7 +24876,7 @@
         <v>46182</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24948,7 +24949,7 @@
         <v>46190</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25026,7 +25027,7 @@
         <v>46199</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25099,7 +25100,7 @@
         <v>46199</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25172,7 +25173,7 @@
         <v>46199</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25245,7 +25246,7 @@
         <v>46199</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25318,7 +25319,7 @@
         <v>46199</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25391,7 +25392,7 @@
         <v>46199</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25464,7 +25465,7 @@
         <v>46199</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25537,7 +25538,7 @@
         <v>46199</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25610,7 +25611,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25683,7 +25684,7 @@
         <v>46204</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25756,7 +25757,7 @@
         <v>46205</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25829,7 +25830,7 @@
         <v>46204</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25902,7 +25903,7 @@
         <v>46216</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25980,7 +25981,7 @@
         <v>46216</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26058,7 +26059,7 @@
         <v>46216</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26136,7 +26137,7 @@
         <v>46268</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26209,7 +26210,7 @@
         <v>46204</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26287,7 +26288,7 @@
         <v>46167</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26360,7 +26361,7 @@
         <v>46273</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26433,7 +26434,7 @@
         <v>46034</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26506,7 +26507,7 @@
         <v>46237</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26584,7 +26585,7 @@
         <v>46237</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26662,7 +26663,7 @@
         <v>46237</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26740,7 +26741,7 @@
         <v>46237</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26818,7 +26819,7 @@
         <v>46237</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26896,7 +26897,7 @@
         <v>46237</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26974,7 +26975,7 @@
         <v>46237</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27052,7 +27053,7 @@
         <v>46237</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27130,7 +27131,7 @@
         <v>46237</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27208,7 +27209,7 @@
         <v>46238</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27281,7 +27282,7 @@
         <v>46238</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27354,7 +27355,7 @@
         <v>46241</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27432,7 +27433,7 @@
         <v>46283</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27505,7 +27506,7 @@
         <v>46244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27583,7 +27584,7 @@
         <v>46244</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27661,7 +27662,7 @@
         <v>46246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27734,7 +27735,7 @@
         <v>46246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27807,7 +27808,7 @@
         <v>46246</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27880,7 +27881,7 @@
         <v>46246</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27953,7 +27954,7 @@
         <v>46246</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28026,7 +28027,7 @@
         <v>46248</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28099,7 +28100,7 @@
         <v>46293</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28177,7 +28178,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28250,7 +28251,7 @@
         <v>46295</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28323,7 +28324,7 @@
         <v>46301</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28401,7 +28402,7 @@
         <v>46301</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28479,7 +28480,7 @@
         <v>46301</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28557,7 +28558,7 @@
         <v>46297</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28635,7 +28636,7 @@
         <v>46261</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28713,7 +28714,7 @@
         <v>44714</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28791,7 +28792,7 @@
         <v>44606</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28864,7 +28865,7 @@
         <v>44722</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28942,7 +28943,7 @@
         <v>45111</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29015,7 +29016,7 @@
         <v>45258</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29093,7 +29094,7 @@
         <v>44714</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29171,7 +29172,7 @@
         <v>44740</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29249,7 +29250,7 @@
         <v>45946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29327,7 +29328,7 @@
         <v>45978</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29405,7 +29406,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45352</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45263</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>46301</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>45105</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>44656</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>45731</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45148</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>45443</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>46203</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45565</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>45272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         <v>44683</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>46301</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3624,7 +3624,7 @@
         <v>46113</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>44593</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         <v>45027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45191</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4084,7 +4084,7 @@
         <v>45190</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45040</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>46253</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>46302</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4534,7 +4534,7 @@
         <v>45049</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45817</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4873,7 +4873,7 @@
         <v>45034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>45002</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>46206</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>46237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5426,7 +5426,7 @@
         <v>44488</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         <v>44827</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44776</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>45392</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45282</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45397</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45197</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>44762</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44816</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>46246</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>45436</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>44937</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>45946</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44862</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44616</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45397</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>45581</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>45195</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44935</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44886</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>45902</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45439</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45911</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45034</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45513</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>45802</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>44696</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45314</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>44778</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45012</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>44967</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45952</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>46038</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9224,7 +9224,7 @@
         <v>46063</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>45952</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         <v>46204</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>46205</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46237</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>46255</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44714</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44656</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>46167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>44585</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44782</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>44648</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>44643</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10578,7 +10578,7 @@
         <v>44757</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10729,7 +10729,7 @@
         <v>44651</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>44757</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44862</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44657</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44839</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45321</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44615</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45702</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45261</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45261</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45525</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45387</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45213</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>44531</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44490</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45518</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>45240</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         <v>45229</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>45562</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45195</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45239</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45258</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44496</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45342</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44982</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45478</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45602</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45758</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45173</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>45583</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45258</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>45279</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>44862</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45478</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45751</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44676</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45700</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13578,7 +13578,7 @@
         <v>45397</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44978</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13724,7 +13724,7 @@
         <v>45894</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45240</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45235</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45896</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45487</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45902</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45156</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45905</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45540</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45225</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45084</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45198</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45241</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45911</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45362</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45916</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45513</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45915</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45425</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15146,7 +15146,7 @@
         <v>45349</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45349</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>44532</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45280</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>44616</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45170</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>45924</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>45545</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44827</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45432</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45126</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>45614</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16052,7 +16052,7 @@
         <v>44869</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16130,7 +16130,7 @@
         <v>45432</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45574</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45160</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45583</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45600</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44686</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44665</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45583</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44814</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45559</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45726</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45082</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>44651</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45096</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45398</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45810</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>44696</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45190</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>44777</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>45427</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45812</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>45427</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>45812</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45812</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>44638</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44956</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18219,7 +18219,7 @@
         <v>45401</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>45272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>45084</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45225</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45478</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45034</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45947</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44979</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>44960</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18891,7 +18891,7 @@
         <v>44960</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18964,7 +18964,7 @@
         <v>44657</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19037,7 +19037,7 @@
         <v>45952</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45952</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45602</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19266,7 +19266,7 @@
         <v>45956</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>45098</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45842</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19490,7 +19490,7 @@
         <v>45159</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>44791</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>45460</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>45582</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>45715</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>45978</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>44805</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45728</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45576</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45677</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45176</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45084</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45875</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45876</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45352</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>45876</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45981</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45084</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45502</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>45346</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>45882</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45728</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45686</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>46098</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>44756</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45173</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45487</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>44610</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45992</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>44998</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44627</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
         <v>45995</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45159</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>44614</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22085,7 +22085,7 @@
         <v>44610</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45002</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>44974</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44839</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44837</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44636</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>44533</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22611,7 +22611,7 @@
         <v>45880</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22689,7 +22689,7 @@
         <v>45876</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45728</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>45894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>44862</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45582</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45010</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45432</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45668</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23293,7 +23293,7 @@
         <v>46041</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>46041</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>46041</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>46041</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>45114</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>46043</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>46043</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45427</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45894</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24063,7 +24063,7 @@
         <v>46058</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24141,7 +24141,7 @@
         <v>45870</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24214,7 +24214,7 @@
         <v>46063</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>46063</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24360,7 +24360,7 @@
         <v>45149</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24506,7 +24506,7 @@
         <v>45747</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24579,7 +24579,7 @@
         <v>45988</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45226</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>46175</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24803,7 +24803,7 @@
         <v>46182</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24876,7 +24876,7 @@
         <v>46182</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24949,7 +24949,7 @@
         <v>46190</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25027,7 +25027,7 @@
         <v>46199</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>46199</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>46199</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>46199</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>46199</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>46199</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>46199</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>46199</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>46204</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>46205</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>46204</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>46216</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>46216</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26059,7 +26059,7 @@
         <v>46216</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26137,7 +26137,7 @@
         <v>46268</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>46204</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46167</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26361,7 +26361,7 @@
         <v>46273</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>46034</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>46237</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>46237</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26663,7 +26663,7 @@
         <v>46237</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>46237</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>46237</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>46237</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46237</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>46237</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>46237</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46238</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>46238</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>46241</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>46283</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>46244</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>46244</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>46246</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         <v>46246</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>46246</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27881,7 +27881,7 @@
         <v>46246</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27954,7 +27954,7 @@
         <v>46246</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         <v>46248</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28100,7 +28100,7 @@
         <v>46293</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>46248</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>46295</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>46301</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>46301</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>46301</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>46297</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28636,7 +28636,7 @@
         <v>46261</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28714,7 +28714,7 @@
         <v>44714</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28792,7 +28792,7 @@
         <v>44606</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28865,7 +28865,7 @@
         <v>44722</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28943,7 +28943,7 @@
         <v>45111</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29016,7 +29016,7 @@
         <v>45258</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29094,7 +29094,7 @@
         <v>44714</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>44740</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>45978</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45992</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>46301</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>46310</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>45105</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44656</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>45443</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45731</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45148</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>45565</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44683</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46113</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45190</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45040</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>46302</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>45034</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45002</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>46206</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45049</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>46237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45817</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>44827</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44816</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>44762</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45392</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45282</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>46246</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45397</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45197</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>45436</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45397</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45581</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45034</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45012</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45911</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44778</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44967</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45952</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45314</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44886</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44696</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>46038</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>46063</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>46204</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>46205</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46237</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45513</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45439</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>46255</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45802</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>46310</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>46167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>44585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44648</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44657</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44862</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44720</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44651</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44839</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44757</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45338</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45425</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44490</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44615</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44956</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45280</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44651</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45487</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>45460</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45432</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45582</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45467</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44686</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45084</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45229</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45176</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45159</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44676</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45346</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45562</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>45726</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45240</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45702</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44974</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44978</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45190</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45427</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44627</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45545</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45173</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44532</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45084</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45010</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45114</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45362</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44862</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45751</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45894</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45352</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44614</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45700</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45876</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44979</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45159</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45156</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44616</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45401</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44533</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45896</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45870</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45894</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45478</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45905</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45427</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45258</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45911</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45915</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45758</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45241</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45677</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45916</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45715</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>45728</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44638</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45239</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45173</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44837</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>44998</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45747</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45947</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45149</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45952</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45952</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45956</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45616</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45978</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45170</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45992</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45583</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44657</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45995</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45226</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45213</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46175</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45261</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45261</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46041</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46041</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>46041</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45084</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46043</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>46043</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45398</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>46182</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>46182</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45225</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44777</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45427</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>46058</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>46063</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>46063</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44916</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45559</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44696</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>46190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44610</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45082</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45582</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>46098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45096</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45342</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45583</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>44869</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44814</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>46202</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>46199</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44665</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>46199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46199</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46199</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46199</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46199</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>46199</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>46204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>46204</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44756</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45880</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45126</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>46205</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45349</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45349</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45478</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45478</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45235</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45195</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45225</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45583</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45084</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45321</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46216</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46216</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>46216</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>46204</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>45397</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>46273</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45387</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46167</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>46034</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>44982</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45487</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45668</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44636</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>46237</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45432</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>46237</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44839</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>46237</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>46237</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46237</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46237</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45502</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>46238</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>46238</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>46237</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45518</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>46283</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45240</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44862</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>46241</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>46244</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>46244</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45272</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>46246</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46246</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45728</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>46246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45258</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>46248</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46293</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46248</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>46295</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45686</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44610</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45198</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>46301</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44496</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>46301</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>46301</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45513</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>44827</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45614</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>46297</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45574</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46261</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45432</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45810</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45812</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45812</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45812</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46268</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44960</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44960</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>46310</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45842</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45576</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45728</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45875</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45876</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45876</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45882</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45111</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44714</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>44606</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45258</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44714</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>44722</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>44740</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45946</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45992</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45263</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>45352</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>45845</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>46301</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2486,7 +2486,7 @@
         <v>46310</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>45105</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44656</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>45443</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>45731</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>45148</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45272</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>45565</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>44683</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>46301</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>46113</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44593</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>45190</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45040</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>45191</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>46253</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>46302</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45002</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4767,7 +4767,7 @@
         <v>45034</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4985,7 +4985,7 @@
         <v>45002</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         <v>46206</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5208,7 +5208,7 @@
         <v>45049</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>46237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>45817</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5543,7 +5543,7 @@
         <v>44488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>44827</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44816</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>44776</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44937</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>44762</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45392</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>45282</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>46246</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45397</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         <v>46262</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>45197</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>45436</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         <v>44937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45946</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>44862</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44616</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45397</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45581</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45195</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45034</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7837,7 +7837,7 @@
         <v>45012</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7942,7 +7942,7 @@
         <v>44935</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>45952</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>45902</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45911</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>44778</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44967</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         <v>45952</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45314</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44886</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44696</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>46038</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>46063</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>46204</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9337,7 +9337,7 @@
         <v>46205</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>46237</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45513</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>45439</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>46255</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45802</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>46310</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>46167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>44585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44648</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44657</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>44862</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44720</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44651</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44839</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44757</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>45338</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>45425</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44490</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44615</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44956</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45602</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45280</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>44651</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45487</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>45460</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>45002</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>45432</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45540</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>45582</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>45602</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44791</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45467</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44686</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>45084</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45229</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45176</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45159</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45196</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44676</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45346</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>45562</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13337,7 +13337,7 @@
         <v>45726</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45240</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45702</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44974</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44978</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>45190</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45034</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45427</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44627</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45545</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45173</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>44532</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14311,7 +14311,7 @@
         <v>45084</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45010</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45114</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45362</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>44862</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14686,7 +14686,7 @@
         <v>45751</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45894</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>45352</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44614</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>45700</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15139,7 +15139,7 @@
         <v>45876</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44979</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15290,7 +15290,7 @@
         <v>45894</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15368,7 +15368,7 @@
         <v>45159</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         <v>45156</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15519,7 +15519,7 @@
         <v>44616</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>45401</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44533</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45896</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45870</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45894</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45902</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>45478</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16128,7 +16128,7 @@
         <v>45905</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45427</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>45258</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45911</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45915</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
         <v>45758</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45241</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45677</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16795,7 +16795,7 @@
         <v>45916</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45715</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16941,7 +16941,7 @@
         <v>45728</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>44638</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17170,7 +17170,7 @@
         <v>45239</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17243,7 +17243,7 @@
         <v>45525</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45173</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>44837</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>44998</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45747</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>45947</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45149</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17764,7 +17764,7 @@
         <v>45978</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45952</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>45952</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45956</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45616</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45988</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>45978</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45170</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45992</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45583</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44657</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45995</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>45226</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45600</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18894,7 +18894,7 @@
         <v>45213</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18967,7 +18967,7 @@
         <v>46175</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45261</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45261</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19196,7 +19196,7 @@
         <v>45279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>46041</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>46041</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>46041</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46041</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45084</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>46043</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>46043</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>45398</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>46182</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19961,7 +19961,7 @@
         <v>46182</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>45225</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44777</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45427</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>46058</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>46063</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>46063</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44916</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45559</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>44696</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>46190</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20789,7 +20789,7 @@
         <v>44610</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45082</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45582</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>46098</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
         <v>45096</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21154,7 +21154,7 @@
         <v>45342</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45583</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>44869</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44814</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>46202</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21529,7 +21529,7 @@
         <v>46199</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21675,7 +21675,7 @@
         <v>44665</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21748,7 +21748,7 @@
         <v>46199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46199</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>46199</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>46199</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22040,7 +22040,7 @@
         <v>46199</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22113,7 +22113,7 @@
         <v>46199</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22186,7 +22186,7 @@
         <v>46204</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>46204</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22332,7 +22332,7 @@
         <v>44756</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45880</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45126</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22561,7 +22561,7 @@
         <v>46205</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45349</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22707,7 +22707,7 @@
         <v>45349</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22780,7 +22780,7 @@
         <v>45478</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>45478</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22936,7 +22936,7 @@
         <v>45235</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23014,7 +23014,7 @@
         <v>45195</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45225</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23165,7 +23165,7 @@
         <v>45583</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45084</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45321</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46216</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46216</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>46216</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>46204</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>45397</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>46273</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45387</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>46167</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>46034</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>44982</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>45487</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45668</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>44636</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>46237</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>46237</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45432</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46237</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>46237</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24748,7 +24748,7 @@
         <v>44839</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>46237</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>46237</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46237</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>46237</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45502</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25206,7 +25206,7 @@
         <v>46238</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25279,7 +25279,7 @@
         <v>46238</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>46237</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>45518</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>46283</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45240</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>44862</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>46241</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>46244</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>46244</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25956,7 +25956,7 @@
         <v>45272</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26029,7 +26029,7 @@
         <v>46246</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>46246</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>45728</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>46246</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>46246</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>46246</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45258</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26550,7 +26550,7 @@
         <v>46248</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26623,7 +26623,7 @@
         <v>46293</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46248</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>46295</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>45686</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26920,7 +26920,7 @@
         <v>44610</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45198</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27071,7 +27071,7 @@
         <v>46301</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>44496</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>46301</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>46301</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45513</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>44827</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>45614</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>46297</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45574</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46261</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45432</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45810</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45812</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45812</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45812</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>46268</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>44960</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>44960</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>46310</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45842</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45576</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>45728</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>45875</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45876</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         <v>45876</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28946,7 +28946,7 @@
         <v>45882</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45111</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44714</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>44606</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29243,7 +29243,7 @@
         <v>45258</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29321,7 +29321,7 @@
         <v>44714</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>44722</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>44740</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29555,7 +29555,7 @@
         <v>45946</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45992</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45352</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45263</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>46310</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>46301</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45105</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44656</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45443</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45731</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45148</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>46301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>46310</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45565</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44683</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46113</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46253</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45040</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45191</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45190</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45049</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>46237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45817</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45002</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45034</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44816</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44827</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45397</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>46246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45197</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>46262</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>45282</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>46310</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44776</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44762</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>45436</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>45946</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44862</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44616</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>45902</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45012</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45911</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44967</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>45397</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45581</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45195</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44935</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>46204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45439</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>46237</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>46038</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44886</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>46063</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45952</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46255</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44696</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44778</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>45034</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45513</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45314</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>44585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44648</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>44862</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44657</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>44720</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44651</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>44839</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>44757</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44610</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45751</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45387</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>45700</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45213</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45195</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45467</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44839</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44837</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44636</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45896</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45902</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45905</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45988</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45728</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45916</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45915</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45010</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45432</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45226</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45668</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45924</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45321</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45196</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45114</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44615</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45229</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45562</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45239</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45525</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45952</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46182</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45952</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>46182</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45240</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45956</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45258</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45478</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>44982</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>46190</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45602</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45758</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45173</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45583</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>46199</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45978</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>46199</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>46199</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>46199</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>46199</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>46199</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>46199</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>46199</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46202</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45981</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>46204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44676</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>46204</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45240</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45992</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>46216</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>46216</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45279</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45995</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>46216</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45225</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>46204</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46167</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45513</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>46034</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>46237</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>46237</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>46237</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>46237</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46237</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>46237</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>46237</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46238</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46238</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44827</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46241</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44862</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45614</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>46283</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45432</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45574</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46041</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>46041</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>46041</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46244</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46244</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>46043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>46043</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>46246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>46246</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45810</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>46246</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>46246</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>46058</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>46246</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45812</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45812</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45812</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>46063</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46063</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>46248</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>46293</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>46248</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>44960</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44960</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>46295</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45842</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>46098</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>45235</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>46301</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45487</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>46301</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46301</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45728</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45576</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>46261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45875</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45876</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45876</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45882</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45540</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45362</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45349</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45349</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>44533</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45880</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>44616</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45876</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>46268</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44862</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45432</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>46273</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44869</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45338</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45427</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45583</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45870</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45583</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45559</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>46297</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45398</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45190</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>44777</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45427</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45149</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>44956</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45747</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45272</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45225</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45478</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45034</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44979</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45602</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45159</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44791</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45677</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45084</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45686</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45173</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44610</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>44916</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45261</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45261</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>44531</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45518</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44496</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45342</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45478</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45397</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>44978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45156</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45084</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45198</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45241</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45425</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>44532</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45280</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45170</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45545</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45616</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45160</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45600</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44686</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44665</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44814</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45726</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45082</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>44651</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44696</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45427</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44638</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45401</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45084</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44657</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45460</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45715</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44805</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45352</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>45084</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45502</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45346</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45728</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44756</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45487</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44998</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44627</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45159</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>44614</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44714</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>44606</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>44722</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>45111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45258</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44714</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>44740</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45946</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45992</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>

--- a/Översikt HALLSBERG.xlsx
+++ b/Översikt HALLSBERG.xlsx
@@ -601,7 +601,7 @@
         <v>45716</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>44617</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>45881</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45352</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>45263</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>44655</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45197</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
         <v>45720</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>46246</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>45316</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>44705</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>45881</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>45610</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         <v>46310</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45845</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>46301</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45105</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44656</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45443</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         <v>46203</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>45731</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>45148</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>46301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>46310</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45565</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45272</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44683</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>46113</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>44593</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>46253</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>46302</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45027</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45040</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45191</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45190</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4770,7 +4770,7 @@
         <v>45049</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
         <v>45981</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>46206</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>46237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>45817</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>45002</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>45034</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45002</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>44816</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44827</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
         <v>45397</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>46246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45197</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>46262</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>45282</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>46310</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>44776</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         <v>45392</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44937</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44762</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
         <v>45436</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7091,7 +7091,7 @@
         <v>44937</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7197,7 +7197,7 @@
         <v>45946</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44862</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44616</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>45902</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45012</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45911</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>44967</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>45952</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>45397</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45581</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>45195</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>44935</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>46204</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>46205</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>45439</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>46237</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>46038</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45802</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>44886</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>46063</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>45952</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>46255</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44696</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9695,7 +9695,7 @@
         <v>44778</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>45034</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45513</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>45314</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>44714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44656</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>46167</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>44585</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>44782</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44648</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44816</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10815,7 +10815,7 @@
         <v>44862</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>44657</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>44720</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>44651</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44757</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>44839</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>44757</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>44610</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45751</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11487,7 +11487,7 @@
         <v>45387</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>45700</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         <v>45213</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11706,7 +11706,7 @@
         <v>45002</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45195</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>45467</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12018,7 +12018,7 @@
         <v>44974</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>44839</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44837</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44636</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45896</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45902</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45905</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>45988</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45728</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45911</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45916</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>45915</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12909,7 +12909,7 @@
         <v>45582</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>45010</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>45432</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45226</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>45668</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>45924</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>45321</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13435,7 +13435,7 @@
         <v>45196</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13513,7 +13513,7 @@
         <v>45114</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13586,7 +13586,7 @@
         <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>46175</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44615</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>45229</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45562</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>45239</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>45525</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45952</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>46182</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>45952</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>46182</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14482,7 +14482,7 @@
         <v>45240</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14555,7 +14555,7 @@
         <v>45956</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>45258</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45478</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>44982</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>46190</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45602</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>45758</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>45173</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15159,7 +15159,7 @@
         <v>45583</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>46199</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45978</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>46199</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>46199</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>46199</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>46199</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>46199</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>46199</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>46199</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>46202</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>45981</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>46204</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44676</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>46205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>46204</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45240</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45992</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45258</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>46216</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>46216</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45279</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45995</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>46216</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16951,7 +16951,7 @@
         <v>45225</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>46204</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46167</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45513</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>46034</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>46237</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>46237</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>46237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>46237</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>46237</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>46237</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>46237</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17867,7 +17867,7 @@
         <v>46237</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>46237</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18023,7 +18023,7 @@
         <v>46238</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>46238</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>44827</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>46241</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>44862</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45614</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18471,7 +18471,7 @@
         <v>46283</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18544,7 +18544,7 @@
         <v>45432</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>45574</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>46041</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>46041</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>46041</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>46041</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>46244</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>46244</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         <v>46043</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>46043</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19319,7 +19319,7 @@
         <v>46246</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19392,7 +19392,7 @@
         <v>46246</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45810</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19538,7 +19538,7 @@
         <v>46246</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>46246</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19684,7 +19684,7 @@
         <v>46058</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>46246</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45812</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>45812</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45812</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20054,7 +20054,7 @@
         <v>46063</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20127,7 +20127,7 @@
         <v>46063</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>46248</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>46293</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20351,7 +20351,7 @@
         <v>46248</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>44960</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20497,7 +20497,7 @@
         <v>44960</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>46295</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20643,7 +20643,7 @@
         <v>45842</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         <v>46098</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
         <v>45235</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>46301</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20950,7 +20950,7 @@
         <v>45487</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21023,7 +21023,7 @@
         <v>46301</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21101,7 +21101,7 @@
         <v>46301</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>45728</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21257,7 +21257,7 @@
         <v>45576</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>46261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>45875</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45876</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>45876</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45882</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45540</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45362</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21851,7 +21851,7 @@
         <v>45349</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21924,7 +21924,7 @@
         <v>45349</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>44533</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45880</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>44616</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45876</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>46268</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45894</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>44862</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45432</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>46273</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>44869</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22757,7 +22757,7 @@
         <v>45338</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45427</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22903,7 +22903,7 @@
         <v>45583</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45894</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23059,7 +23059,7 @@
         <v>45870</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23132,7 +23132,7 @@
         <v>45583</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45559</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>46297</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45398</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45190</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>44777</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45427</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45149</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>44956</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45747</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45272</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45225</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45478</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45034</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>44979</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45602</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45159</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44791</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>45582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45677</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45176</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45084</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45686</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45173</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>44610</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>44916</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>45261</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45261</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>44531</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45518</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>44496</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45342</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45478</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45397</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>44978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45156</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45084</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45198</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45241</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45425</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>44532</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45280</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45170</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45545</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45616</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>45160</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26726,7 +26726,7 @@
         <v>45600</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44686</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>44665</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>44814</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>45726</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>45082</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>44651</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45096</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>44696</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45427</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27471,7 +27471,7 @@
         <v>44638</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>45401</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45084</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>44657</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45460</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>45715</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44805</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45352</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28138,7 +28138,7 @@
         <v>45084</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28216,7 +28216,7 @@
         <v>45502</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28289,7 +28289,7 @@
         <v>45346</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45728</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28440,7 +28440,7 @@
         <v>44756</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28513,7 +28513,7 @@
         <v>45487</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28586,7 +28586,7 @@
         <v>44998</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28659,7 +28659,7 @@
         <v>44627</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28732,7 +28732,7 @@
         <v>45159</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>44614</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28878,7 +28878,7 @@
         <v>44714</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>44606</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>44722</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29107,7 +29107,7 @@
         <v>45111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45258</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>44714</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29336,7 +29336,7 @@
         <v>44740</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29414,7 +29414,7 @@
         <v>45946</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45992</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
